--- a/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_35.xlsx
+++ b/model/Outputs/11. Interest rate/10/Output Files/0.2/Output_12_35.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2036747.632277953</v>
+        <v>2037818.755990225</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14697842.82031877</v>
+        <v>14697842.82031956</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14697842.82031877</v>
+        <v>14697842.82031956</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>657188.6984935161</v>
+        <v>657188.6984941057</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>657188.6984935161</v>
+        <v>657188.6984941057</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>31155692.28278475</v>
+        <v>31155692.28278463</v>
       </c>
     </row>
   </sheetData>
@@ -669,10 +669,10 @@
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.34732203575993</v>
+        <v>5.146009903586449</v>
       </c>
       <c r="H2" t="n">
-        <v>5.608919435675552</v>
+        <v>3.81023156784903</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>97.51785512532402</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G3" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,16 +778,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>374</v>
+        <v>133.6519859716245</v>
       </c>
       <c r="S3" t="n">
         <v>62.48881128536601</v>
       </c>
       <c r="T3" t="n">
-        <v>264.6398022383472</v>
+        <v>374</v>
       </c>
       <c r="U3" t="n">
         <v>0.1959257979225981</v>
@@ -909,10 +909,10 @@
         <v>3.347322035759929</v>
       </c>
       <c r="H5" t="n">
-        <v>5.608919435675665</v>
+        <v>3.810231567849018</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1.798687867826647</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -985,13 +985,13 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>241.0084251213388</v>
       </c>
       <c r="I6" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1015,10 +1015,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>258.5703075255113</v>
+        <v>374</v>
       </c>
       <c r="S6" t="n">
         <v>62.48881128536602</v>
@@ -1027,13 +1027,13 @@
         <v>4.473444462796834</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1959257979225968</v>
+        <v>374</v>
       </c>
       <c r="V6" t="n">
-        <v>374</v>
+        <v>14.51066719152016</v>
       </c>
       <c r="W6" t="n">
-        <v>374</v>
+        <v>32.37314290982852</v>
       </c>
       <c r="X6" t="n">
         <v>19.86273944538755</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.798687867826661</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>85.50414770182039</v>
+        <v>87.30283556964716</v>
       </c>
       <c r="T8" t="n">
         <v>184.8805867536895</v>
@@ -1207,28 +1207,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>348.9870716648493</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1252,7 +1252,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>145.073529241423</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>133.6519859716245</v>
@@ -1264,7 +1264,7 @@
         <v>4.473444462796863</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1959257979225981</v>
+        <v>374</v>
       </c>
       <c r="V9" t="n">
         <v>14.51066719152016</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>254.6318692699711</v>
       </c>
     </row>
     <row r="10">
@@ -1374,16 +1374,16 @@
         <v>91.33915573984979</v>
       </c>
       <c r="E11" t="n">
-        <v>84.66720461037373</v>
+        <v>85.36328960686865</v>
       </c>
       <c r="F11" t="n">
         <v>85.88962870801186</v>
       </c>
       <c r="G11" t="n">
-        <v>83.28199540259411</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H11" t="n">
-        <v>73.89995518593948</v>
+        <v>73.2038701894446</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1444,7 +1444,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C12" t="n">
         <v>42.09991244551929</v>
@@ -1453,19 +1453,19 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F12" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G12" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H12" t="n">
-        <v>324.5441815260438</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -1492,19 +1492,19 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S12" t="n">
-        <v>355.8435840456416</v>
+        <v>451.901311285366</v>
       </c>
       <c r="T12" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U12" t="n">
-        <v>400.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V12" t="n">
-        <v>95.51066719152016</v>
+        <v>128.5053276453525</v>
       </c>
       <c r="W12" t="n">
         <v>113.3731429098285</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M13" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N13" t="n">
         <v>150.9111244520127</v>
@@ -1571,10 +1571,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>377.845046013938</v>
+        <v>374.9946845364717</v>
       </c>
       <c r="S13" t="n">
-        <v>28.98969199588089</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1617,10 +1617,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G14" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H14" t="n">
-        <v>73.89995518593948</v>
+        <v>73.20387018944457</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1681,13 +1681,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C15" t="n">
         <v>361.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>347.9376868977026</v>
+        <v>251.8799596579782</v>
       </c>
       <c r="E15" t="n">
         <v>23.67209722191262</v>
@@ -1696,10 +1696,10 @@
         <v>20.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H15" t="n">
-        <v>5.544181526043773</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1750,7 +1750,7 @@
         <v>100.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>303.3336655264099</v>
+        <v>80.39139276613435</v>
       </c>
     </row>
     <row r="16">
@@ -1811,7 +1811,7 @@
         <v>377.845046013938</v>
       </c>
       <c r="S16" t="n">
-        <v>28.98969199588179</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1854,10 +1854,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G17" t="n">
-        <v>82.58591040609919</v>
+        <v>83.28199540259408</v>
       </c>
       <c r="H17" t="n">
-        <v>73.89995518593946</v>
+        <v>73.2038701894446</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -1918,13 +1918,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C18" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E18" t="n">
         <v>23.67209722191262</v>
@@ -1966,13 +1966,13 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>179.2619859716245</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S18" t="n">
-        <v>132.901311285366</v>
+        <v>451.901311285366</v>
       </c>
       <c r="T18" t="n">
-        <v>83.17594446279685</v>
+        <v>402.1759444627968</v>
       </c>
       <c r="U18" t="n">
         <v>81.15842579792258</v>
@@ -1987,7 +1987,7 @@
         <v>100.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>303.3336655264099</v>
+        <v>303.33366552641</v>
       </c>
     </row>
     <row r="19">
@@ -2048,7 +2048,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S19" t="n">
-        <v>28.9896919958823</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -2091,10 +2091,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G20" t="n">
-        <v>83.28199540259408</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H20" t="n">
-        <v>73.89995518593946</v>
+        <v>73.20387018944457</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T20" t="n">
         <v>261.2171194170061</v>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>384.5565566463266</v>
+        <v>65.55655664632661</v>
       </c>
       <c r="C21" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D21" t="n">
         <v>28.93768689770263</v>
@@ -2167,13 +2167,13 @@
         <v>23.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>20.63624233787687</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G21" t="n">
-        <v>5.950139648612264</v>
+        <v>5.950139648612248</v>
       </c>
       <c r="H21" t="n">
-        <v>5.544181526043758</v>
+        <v>5.544181526043773</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,16 +2203,16 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>179.2619859716245</v>
+        <v>179.2619859716246</v>
       </c>
       <c r="S21" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T21" t="n">
-        <v>83.17594446279685</v>
+        <v>306.1182172230725</v>
       </c>
       <c r="U21" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V21" t="n">
         <v>95.51066719152016</v>
@@ -2221,7 +2221,7 @@
         <v>113.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>323.805012205663</v>
+        <v>100.8627394453875</v>
       </c>
       <c r="Y21" t="n">
         <v>399.3913927661343</v>
@@ -2264,10 +2264,10 @@
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>6.155529797123449</v>
+        <v>6.155529797123435</v>
       </c>
       <c r="M22" t="n">
-        <v>97.89093927140237</v>
+        <v>97.89093927140236</v>
       </c>
       <c r="N22" t="n">
         <v>150.9111244520127</v>
@@ -2282,10 +2282,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>377.8450460139379</v>
+        <v>377.845046013938</v>
       </c>
       <c r="S22" t="n">
-        <v>28.98969199588095</v>
+        <v>28.98969199588089</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>141.5319320520589</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T23" t="n">
         <v>261.2171194170061</v>
@@ -2379,7 +2379,7 @@
         <v>319.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>273.2818334606677</v>
+        <v>272.5857484641728</v>
       </c>
       <c r="Y23" t="n">
         <v>192.3174326828064</v>
@@ -2395,16 +2395,16 @@
         <v>65.55655664632661</v>
       </c>
       <c r="C24" t="n">
-        <v>265.042185205795</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>28.93768689770263</v>
       </c>
       <c r="E24" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F24" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G24" t="n">
         <v>5.950139648612264</v>
@@ -2440,7 +2440,7 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>179.2619859716245</v>
+        <v>498.2619859716245</v>
       </c>
       <c r="S24" t="n">
         <v>132.901311285366</v>
@@ -2449,10 +2449,10 @@
         <v>83.17594446279685</v>
       </c>
       <c r="U24" t="n">
-        <v>81.15842579792258</v>
+        <v>400.1584257979226</v>
       </c>
       <c r="V24" t="n">
-        <v>95.51066719152016</v>
+        <v>318.4529399517959</v>
       </c>
       <c r="W24" t="n">
         <v>113.3731429098285</v>
@@ -2501,7 +2501,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>3.305168319657098</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M25" t="n">
         <v>97.89093927140237</v>
@@ -2522,7 +2522,7 @@
         <v>377.8450460139379</v>
       </c>
       <c r="S25" t="n">
-        <v>31.84005347334727</v>
+        <v>28.98969199588095</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2565,10 +2565,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G26" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H26" t="n">
-        <v>73.89995518593948</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2601,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>141.5319320525037</v>
+        <v>142.2280170485541</v>
       </c>
       <c r="T26" t="n">
         <v>261.2171194170061</v>
@@ -2632,22 +2632,22 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C27" t="n">
-        <v>361.0999124455193</v>
+        <v>42.09991244551929</v>
       </c>
       <c r="D27" t="n">
         <v>28.93768689770263</v>
       </c>
       <c r="E27" t="n">
-        <v>23.67209722191262</v>
+        <v>246.6143699821882</v>
       </c>
       <c r="F27" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G27" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H27" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
@@ -2677,22 +2677,22 @@
         <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S27" t="n">
         <v>132.901311285366</v>
       </c>
       <c r="T27" t="n">
-        <v>83.17594446279683</v>
+        <v>402.1759444627968</v>
       </c>
       <c r="U27" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V27" t="n">
         <v>95.51066719152016</v>
       </c>
       <c r="W27" t="n">
-        <v>336.3154156701039</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X27" t="n">
         <v>100.8627394453875</v>
@@ -2738,10 +2738,10 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>3.305168319657323</v>
+        <v>3.305168319657098</v>
       </c>
       <c r="M28" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N28" t="n">
         <v>150.9111244520127</v>
@@ -2756,10 +2756,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S28" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2802,10 +2802,10 @@
         <v>85.88962870801186</v>
       </c>
       <c r="G29" t="n">
-        <v>83.28199540259411</v>
+        <v>82.58591040609919</v>
       </c>
       <c r="H29" t="n">
-        <v>73.20387018988927</v>
+        <v>73.89995518593946</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2875,16 +2875,16 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E30" t="n">
-        <v>23.67209722191262</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F30" t="n">
-        <v>339.6362423378769</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G30" t="n">
-        <v>5.950139648612248</v>
+        <v>5.950139648612264</v>
       </c>
       <c r="H30" t="n">
-        <v>5.544181526043773</v>
+        <v>5.544181526043758</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
@@ -2914,28 +2914,28 @@
         <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>179.2619859716246</v>
+        <v>179.2619859716245</v>
       </c>
       <c r="S30" t="n">
-        <v>355.8435840456414</v>
+        <v>451.901311285366</v>
       </c>
       <c r="T30" t="n">
-        <v>83.17594446279683</v>
+        <v>83.17594446279685</v>
       </c>
       <c r="U30" t="n">
-        <v>81.1584257979226</v>
+        <v>81.15842579792258</v>
       </c>
       <c r="V30" t="n">
-        <v>414.5106671915202</v>
+        <v>95.51066719152016</v>
       </c>
       <c r="W30" t="n">
-        <v>432.3731429098285</v>
+        <v>113.3731429098285</v>
       </c>
       <c r="X30" t="n">
-        <v>100.8627394453875</v>
+        <v>419.8627394453875</v>
       </c>
       <c r="Y30" t="n">
-        <v>80.39139276613435</v>
+        <v>303.3336655264098</v>
       </c>
     </row>
     <row r="31">
@@ -2975,13 +2975,13 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>6.155529797123435</v>
+        <v>6.155529797123449</v>
       </c>
       <c r="M31" t="n">
-        <v>97.89093927140236</v>
+        <v>97.89093927140237</v>
       </c>
       <c r="N31" t="n">
-        <v>148.0607629745466</v>
+        <v>148.0607629745464</v>
       </c>
       <c r="O31" t="n">
         <v>227.9026788331133</v>
@@ -2993,10 +2993,10 @@
         <v>351.422266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>377.845046013938</v>
+        <v>377.8450460139379</v>
       </c>
       <c r="S31" t="n">
-        <v>31.84005347334724</v>
+        <v>31.84005347334727</v>
       </c>
       <c r="T31" t="n">
         <v>0</v>
@@ -3036,10 +3036,10 @@
         <v>85.36328960686865</v>
       </c>
       <c r="F32" t="n">
-        <v>85.88962870801186</v>
+        <v>85.19354371151695</v>
       </c>
       <c r="G32" t="n">
-        <v>82.5859104065439</v>
+        <v>83.28199540259411</v>
       </c>
       <c r="H32" t="n">
         <v>73.89995518593948</v>
@@ -3112,13 +3112,13 @@
         <v>28.93768689770263</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>23.67209722191262</v>
       </c>
       <c r="F33" t="n">
-        <v>243.5785150981524</v>
+        <v>20.63624233787687</v>
       </c>
       <c r="G33" t="n">
-        <v>5.950139648612248</v>
+        <v>324.9501396486123</v>
       </c>
       <c r="H33" t="n">
         <v>5.544181526043773</v>
@@ -3157,7 +3157,7 @@
         <v>132.901311285366</v>
       </c>
       <c r="T33" t="n">
-        <v>83.17594446279683</v>
+        <v>306.1182172230725</v>
       </c>
       <c r="U33" t="n">
         <v>81.1584257979226</v>
@@ -3224,13 +3224,13 @@
         <v>227.9026788331133</v>
       </c>
       <c r="P34" t="n">
-        <v>285.5554374901558</v>
+        <v>288.4057989676218</v>
       </c>
       <c r="Q34" t="n">
         <v>351.422266425598</v>
       </c>
       <c r="R34" t="n">
-        <v>377.845046013938</v>
+        <v>374.9946845364717</v>
       </c>
       <c r="S34" t="n">
         <v>31.84005347334724</v>
@@ -3273,10 +3273,10 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F35" t="n">
-        <v>4.588698897749918</v>
+        <v>7.889628708011855</v>
       </c>
       <c r="G35" t="n">
-        <v>5.2819954025941</v>
+        <v>5.281995402594077</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -3312,7 +3312,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>64.22801704855405</v>
+        <v>60.92708723799848</v>
       </c>
       <c r="T35" t="n">
         <v>183.2171194170061</v>
@@ -3346,13 +3346,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>347.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -3385,31 +3385,31 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>72.31352924142297</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>360.2105053578924</v>
+        <v>101.2619859716245</v>
       </c>
       <c r="S36" t="n">
-        <v>54.90131128536602</v>
+        <v>54.90131128536603</v>
       </c>
       <c r="T36" t="n">
-        <v>5.175944462796835</v>
+        <v>5.175944462796849</v>
       </c>
       <c r="U36" t="n">
-        <v>3.158425797922597</v>
+        <v>3.158425797922575</v>
       </c>
       <c r="V36" t="n">
-        <v>17.51066719152016</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="W36" t="n">
-        <v>35.37314290982852</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="X36" t="n">
-        <v>22.86273944538755</v>
+        <v>164.9215324822299</v>
       </c>
       <c r="Y36" t="n">
-        <v>2.391392766134345</v>
+        <v>374.0000000000201</v>
       </c>
     </row>
     <row r="37">
@@ -3452,10 +3452,10 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>19.89093927140236</v>
+        <v>19.89093927140237</v>
       </c>
       <c r="N37" t="n">
-        <v>72.91112445201273</v>
+        <v>72.9111244520127</v>
       </c>
       <c r="O37" t="n">
         <v>149.9026788331133</v>
@@ -3467,7 +3467,7 @@
         <v>273.422266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>299.845046013938</v>
+        <v>299.8450460139379</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>7.363289606868648</v>
       </c>
       <c r="F38" t="n">
-        <v>4.588698897901185</v>
+        <v>7.889628708011855</v>
       </c>
       <c r="G38" t="n">
         <v>5.2819954025941</v>
@@ -3555,7 +3555,7 @@
         <v>183.2171194170061</v>
       </c>
       <c r="U38" t="n">
-        <v>252.1032663978569</v>
+        <v>248.8023365873013</v>
       </c>
       <c r="V38" t="n">
         <v>232.8510241668239</v>
@@ -3577,25 +3577,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>374.0000000001074</v>
+        <v>0</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
-        <v>145.0194725247581</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0</v>
+        <v>175.2018093001536</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>324.5441815260438</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
@@ -3640,10 +3640,10 @@
         <v>17.51066719152016</v>
       </c>
       <c r="W39" t="n">
-        <v>374.0000000001074</v>
+        <v>35.37314290982852</v>
       </c>
       <c r="X39" t="n">
-        <v>374.0000000001074</v>
+        <v>22.86273944538755</v>
       </c>
       <c r="Y39" t="n">
         <v>2.391392766134345</v>
@@ -3735,22 +3735,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>50.73291375378185</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F41" t="n">
         <v>0</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>109.2819954025941</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -3795,13 +3795,13 @@
         <v>356.1032663978569</v>
       </c>
       <c r="V41" t="n">
-        <v>336.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
-        <v>194.7740007720102</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y41" t="n">
         <v>218.3174326828064</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.386773445870167</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
         <v>205.2619859716246</v>
@@ -3868,7 +3868,7 @@
         <v>158.901311285366</v>
       </c>
       <c r="T42" t="n">
-        <v>109.1759444627968</v>
+        <v>111.562717908222</v>
       </c>
       <c r="U42" t="n">
         <v>107.1584257979226</v>
@@ -3923,28 +3923,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>32.15552979712344</v>
+        <v>1.555623315583416</v>
       </c>
       <c r="M43" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N43" t="n">
-        <v>176.9111244520127</v>
+        <v>0</v>
       </c>
       <c r="O43" t="n">
-        <v>253.9026788331133</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>314.4057989676218</v>
       </c>
       <c r="Q43" t="n">
-        <v>220.5354044354171</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>57.84005347334724</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -3972,25 +3972,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0</v>
+        <v>188.9993129555745</v>
       </c>
       <c r="C44" t="n">
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>117.3391557398498</v>
       </c>
       <c r="E44" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>111.8896287080119</v>
+        <v>74.26096221837268</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>109.2819954025941</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>99.89995518593946</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -4026,22 +4026,22 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>287.2171194170061</v>
       </c>
       <c r="U44" t="n">
         <v>356.1032663978569</v>
       </c>
       <c r="V44" t="n">
-        <v>227.4077058460922</v>
+        <v>0</v>
       </c>
       <c r="W44" t="n">
-        <v>345.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>299.2818334606677</v>
+        <v>0</v>
       </c>
       <c r="Y44" t="n">
-        <v>0</v>
+        <v>218.3174326828064</v>
       </c>
     </row>
     <row r="45">
@@ -4096,7 +4096,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.386773445870167</v>
+        <v>2.386773445425144</v>
       </c>
       <c r="R45" t="n">
         <v>205.2619859716245</v>
@@ -4163,22 +4163,22 @@
         <v>32.15552979712345</v>
       </c>
       <c r="M46" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N46" t="n">
-        <v>89.49741468537025</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O46" t="n">
         <v>253.9026788331133</v>
       </c>
       <c r="P46" t="n">
-        <v>314.4057989676218</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>103.101149929539</v>
       </c>
       <c r="R46" t="n">
-        <v>374.0000000001147</v>
+        <v>374.0000000001529</v>
       </c>
       <c r="S46" t="n">
         <v>57.84005347334727</v>
@@ -4312,7 +4312,7 @@
         <v>38.96670855700554</v>
       </c>
       <c r="G2" t="n">
-        <v>35.58557518755106</v>
+        <v>33.76871875540306</v>
       </c>
       <c r="H2" t="n">
         <v>29.92</v>
@@ -4321,25 +4321,25 @@
         <v>29.92</v>
       </c>
       <c r="J2" t="n">
-        <v>269.5197546733668</v>
+        <v>400.18</v>
       </c>
       <c r="K2" t="n">
-        <v>321.1580850251256</v>
+        <v>770.4399999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>385.22</v>
+        <v>834.5019149748742</v>
       </c>
       <c r="M2" t="n">
-        <v>385.22</v>
+        <v>834.5019149748744</v>
       </c>
       <c r="N2" t="n">
-        <v>755.48</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O2" t="n">
+        <v>1067.648108133742</v>
+      </c>
+      <c r="P2" t="n">
         <v>1125.74</v>
-      </c>
-      <c r="P2" t="n">
-        <v>1496</v>
       </c>
       <c r="Q2" t="n">
         <v>1496</v>
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>573.6316988789948</v>
+        <v>474.703765048839</v>
       </c>
       <c r="C3" t="n">
-        <v>573.6316988789948</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="D3" t="n">
-        <v>573.6316988789948</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="E3" t="n">
-        <v>573.6316988789948</v>
+        <v>376.2008810838653</v>
       </c>
       <c r="F3" t="n">
-        <v>573.6316988789948</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="G3" t="n">
-        <v>244.8234770117097</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="H3" t="n">
-        <v>244.8234770117097</v>
+        <v>33.13396963146437</v>
       </c>
       <c r="I3" t="n">
         <v>33.13396963146437</v>
@@ -4421,31 +4421,31 @@
         <v>1496</v>
       </c>
       <c r="Q3" t="n">
-        <v>1349.46108157432</v>
+        <v>1496</v>
       </c>
       <c r="R3" t="n">
-        <v>971.6833037965423</v>
+        <v>1360.997993968056</v>
       </c>
       <c r="S3" t="n">
-        <v>908.5632923971827</v>
+        <v>1297.877982568697</v>
       </c>
       <c r="T3" t="n">
-        <v>641.2503608432967</v>
+        <v>920.1002047909187</v>
       </c>
       <c r="U3" t="n">
-        <v>641.0524559969102</v>
+        <v>919.9022999445323</v>
       </c>
       <c r="V3" t="n">
-        <v>626.3952164095161</v>
+        <v>905.2450603571382</v>
       </c>
       <c r="W3" t="n">
-        <v>593.695072056154</v>
+        <v>872.5449160037761</v>
       </c>
       <c r="X3" t="n">
-        <v>573.6316988789948</v>
+        <v>852.4815428266169</v>
       </c>
       <c r="Y3" t="n">
-        <v>573.6316988789948</v>
+        <v>852.4815428266169</v>
       </c>
     </row>
     <row r="4">
@@ -4455,34 +4455,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>465.4012323549126</v>
+        <v>587.0598556495411</v>
       </c>
       <c r="C4" t="n">
-        <v>591.4032381733484</v>
+        <v>713.0618614679769</v>
       </c>
       <c r="D4" t="n">
-        <v>704.7223822983485</v>
+        <v>826.381005592977</v>
       </c>
       <c r="E4" t="n">
-        <v>822.5512865097616</v>
+        <v>857.4784261700831</v>
       </c>
       <c r="F4" t="n">
-        <v>822.5512865097616</v>
+        <v>857.4784261700831</v>
       </c>
       <c r="G4" t="n">
-        <v>822.5512865097616</v>
+        <v>857.4784261700831</v>
       </c>
       <c r="H4" t="n">
-        <v>822.5512865097616</v>
+        <v>1028.614002149153</v>
       </c>
       <c r="I4" t="n">
-        <v>1049.160261183549</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="J4" t="n">
-        <v>1251.462556240126</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K4" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L4" t="n">
         <v>1386.743548464727</v>
@@ -4506,25 +4506,25 @@
         <v>29.92</v>
       </c>
       <c r="S4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="T4" t="n">
-        <v>70.34367574991084</v>
+        <v>29.92</v>
       </c>
       <c r="U4" t="n">
-        <v>70.34367574991084</v>
+        <v>276.481125097303</v>
       </c>
       <c r="V4" t="n">
-        <v>70.34367574991084</v>
+        <v>475.302517983249</v>
       </c>
       <c r="W4" t="n">
-        <v>242.2345940095882</v>
+        <v>475.302517983249</v>
       </c>
       <c r="X4" t="n">
-        <v>242.2345940095882</v>
+        <v>475.302517983249</v>
       </c>
       <c r="Y4" t="n">
-        <v>353.6438946886205</v>
+        <v>475.302517983249</v>
       </c>
     </row>
     <row r="5">
@@ -4552,7 +4552,7 @@
         <v>35.58557518755118</v>
       </c>
       <c r="H5" t="n">
-        <v>29.92</v>
+        <v>31.73685643214813</v>
       </c>
       <c r="I5" t="n">
         <v>29.92</v>
@@ -4561,22 +4561,22 @@
         <v>29.92</v>
       </c>
       <c r="K5" t="n">
-        <v>263.0661931588676</v>
+        <v>81.5583303517588</v>
       </c>
       <c r="L5" t="n">
-        <v>327.128108133742</v>
+        <v>145.6202453266332</v>
       </c>
       <c r="M5" t="n">
-        <v>697.388108133742</v>
+        <v>385.22</v>
       </c>
       <c r="N5" t="n">
-        <v>1067.648108133742</v>
+        <v>755.48</v>
       </c>
       <c r="O5" t="n">
-        <v>1067.648108133742</v>
+        <v>1125.74</v>
       </c>
       <c r="P5" t="n">
-        <v>1125.74</v>
+        <v>1496</v>
       </c>
       <c r="Q5" t="n">
         <v>1496</v>
@@ -4613,25 +4613,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>241.6095073802453</v>
+        <v>602.1710755252032</v>
       </c>
       <c r="C6" t="n">
-        <v>241.6095073802453</v>
+        <v>602.1710755252032</v>
       </c>
       <c r="D6" t="n">
-        <v>241.6095073802453</v>
+        <v>602.1710755252032</v>
       </c>
       <c r="E6" t="n">
-        <v>241.6095073802453</v>
+        <v>602.1710755252032</v>
       </c>
       <c r="F6" t="n">
-        <v>241.6095073802453</v>
+        <v>602.1710755252032</v>
       </c>
       <c r="G6" t="n">
-        <v>241.6095073802453</v>
+        <v>273.362853657918</v>
       </c>
       <c r="H6" t="n">
-        <v>241.6095073802453</v>
+        <v>29.92</v>
       </c>
       <c r="I6" t="n">
         <v>29.92</v>
@@ -4658,31 +4658,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q6" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R6" t="n">
-        <v>1085.064983129208</v>
+        <v>1115.008252590758</v>
       </c>
       <c r="S6" t="n">
-        <v>1021.944971729848</v>
+        <v>1051.888241191398</v>
       </c>
       <c r="T6" t="n">
-        <v>1017.426340959346</v>
+        <v>1047.369610420896</v>
       </c>
       <c r="U6" t="n">
-        <v>1017.22843611296</v>
+        <v>669.5918326431186</v>
       </c>
       <c r="V6" t="n">
-        <v>639.4506583351822</v>
+        <v>654.9345930557245</v>
       </c>
       <c r="W6" t="n">
-        <v>261.6728805574044</v>
+        <v>622.2344487023623</v>
       </c>
       <c r="X6" t="n">
-        <v>241.6095073802453</v>
+        <v>602.1710755252032</v>
       </c>
       <c r="Y6" t="n">
-        <v>241.6095073802453</v>
+        <v>602.1710755252032</v>
       </c>
     </row>
     <row r="7">
@@ -4692,34 +4692,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>774.8297405151413</v>
+        <v>574.6797468089894</v>
       </c>
       <c r="C7" t="n">
-        <v>900.8317463335771</v>
+        <v>574.6797468089894</v>
       </c>
       <c r="D7" t="n">
-        <v>1014.150890458577</v>
+        <v>687.9988909339895</v>
       </c>
       <c r="E7" t="n">
-        <v>1131.97979466999</v>
+        <v>687.9988909339895</v>
       </c>
       <c r="F7" t="n">
-        <v>1256.340767261926</v>
+        <v>687.9988909339895</v>
       </c>
       <c r="G7" t="n">
-        <v>1386.743548464727</v>
+        <v>841.5875519028421</v>
       </c>
       <c r="H7" t="n">
-        <v>1386.743548464727</v>
+        <v>1012.723127881912</v>
       </c>
       <c r="I7" t="n">
-        <v>1386.743548464727</v>
+        <v>1012.723127881912</v>
       </c>
       <c r="J7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="K7" t="n">
-        <v>1386.743548464727</v>
+        <v>1382.983127881912</v>
       </c>
       <c r="L7" t="n">
         <v>1386.743548464727</v>
@@ -4743,25 +4743,25 @@
         <v>29.92</v>
       </c>
       <c r="S7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991083</v>
       </c>
       <c r="T7" t="n">
-        <v>29.92</v>
+        <v>70.34367574991083</v>
       </c>
       <c r="U7" t="n">
-        <v>29.92</v>
+        <v>316.9048008472139</v>
       </c>
       <c r="V7" t="n">
-        <v>228.741392885946</v>
+        <v>462.9224091426973</v>
       </c>
       <c r="W7" t="n">
-        <v>400.6323111456234</v>
+        <v>462.9224091426973</v>
       </c>
       <c r="X7" t="n">
-        <v>551.6631021698169</v>
+        <v>462.9224091426973</v>
       </c>
       <c r="Y7" t="n">
-        <v>663.0724028488492</v>
+        <v>462.9224091426973</v>
       </c>
     </row>
     <row r="8">
@@ -4795,31 +4795,31 @@
         <v>29.92</v>
       </c>
       <c r="J8" t="n">
-        <v>29.92</v>
+        <v>400.18</v>
       </c>
       <c r="K8" t="n">
-        <v>400.18</v>
+        <v>451.8183303517587</v>
       </c>
       <c r="L8" t="n">
-        <v>464.2419149748744</v>
+        <v>515.8802453266331</v>
       </c>
       <c r="M8" t="n">
-        <v>834.5019149748744</v>
+        <v>697.388108133742</v>
       </c>
       <c r="N8" t="n">
-        <v>1204.761914974874</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="O8" t="n">
-        <v>1204.761914974874</v>
+        <v>1067.648108133742</v>
       </c>
       <c r="P8" t="n">
-        <v>1262.853806841132</v>
+        <v>1125.74</v>
       </c>
       <c r="Q8" t="n">
         <v>1496</v>
       </c>
       <c r="R8" t="n">
-        <v>1494.183143567852</v>
+        <v>1496</v>
       </c>
       <c r="S8" t="n">
         <v>1407.815317606417</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>723.4756081758906</v>
+        <v>587.7429389175309</v>
       </c>
       <c r="C9" t="n">
-        <v>358.7282218672851</v>
+        <v>587.7429389175309</v>
       </c>
       <c r="D9" t="n">
-        <v>358.7282218672851</v>
+        <v>587.7429389175309</v>
       </c>
       <c r="E9" t="n">
-        <v>358.7282218672851</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="F9" t="n">
-        <v>358.7282218672851</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="G9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="H9" t="n">
-        <v>29.92</v>
+        <v>241.6095073802453</v>
       </c>
       <c r="I9" t="n">
         <v>29.92</v>
@@ -4895,31 +4895,31 @@
         <v>1492.786030368536</v>
       </c>
       <c r="Q9" t="n">
-        <v>1346.247111942856</v>
+        <v>1492.786030368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1211.245105910912</v>
+        <v>1357.784024336592</v>
       </c>
       <c r="S9" t="n">
-        <v>1148.125094511552</v>
+        <v>1294.664012937232</v>
       </c>
       <c r="T9" t="n">
-        <v>1143.60646374105</v>
+        <v>1290.14538216673</v>
       </c>
       <c r="U9" t="n">
-        <v>1143.408558894664</v>
+        <v>912.3676043889525</v>
       </c>
       <c r="V9" t="n">
-        <v>1128.75131930727</v>
+        <v>897.7103648015584</v>
       </c>
       <c r="W9" t="n">
-        <v>1096.051174953908</v>
+        <v>865.0102204481963</v>
       </c>
       <c r="X9" t="n">
-        <v>1075.987801776748</v>
+        <v>844.9468472710371</v>
       </c>
       <c r="Y9" t="n">
-        <v>1075.987801776748</v>
+        <v>587.7429389175309</v>
       </c>
     </row>
     <row r="10">
@@ -4929,34 +4929,34 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>576.0083476291953</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="C10" t="n">
-        <v>702.0103534476311</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="D10" t="n">
-        <v>815.3294975726312</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="E10" t="n">
-        <v>815.3294975726312</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="F10" t="n">
-        <v>939.6904701645667</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="G10" t="n">
-        <v>1093.279131133419</v>
+        <v>618.9235078479112</v>
       </c>
       <c r="H10" t="n">
-        <v>1264.414707112489</v>
+        <v>658.3540021491528</v>
       </c>
       <c r="I10" t="n">
-        <v>1382.983127881912</v>
+        <v>884.9629768229406</v>
       </c>
       <c r="J10" t="n">
-        <v>1382.983127881912</v>
+        <v>1255.222976822941</v>
       </c>
       <c r="K10" t="n">
-        <v>1382.983127881912</v>
+        <v>1386.743548464727</v>
       </c>
       <c r="L10" t="n">
         <v>1386.743548464727</v>
@@ -4983,22 +4983,22 @@
         <v>29.92</v>
       </c>
       <c r="T10" t="n">
-        <v>29.92</v>
+        <v>218.7737217817557</v>
       </c>
       <c r="U10" t="n">
-        <v>29.92</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="V10" t="n">
-        <v>29.92</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="W10" t="n">
-        <v>201.8109182596774</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="X10" t="n">
-        <v>352.841709283871</v>
+        <v>465.3348468790587</v>
       </c>
       <c r="Y10" t="n">
-        <v>464.2510099629032</v>
+        <v>465.3348468790587</v>
       </c>
     </row>
     <row r="11">
@@ -5017,13 +5017,13 @@
         <v>383.4492766736557</v>
       </c>
       <c r="E11" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F11" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G11" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H11" t="n">
         <v>52.4</v>
@@ -5032,25 +5032,25 @@
         <v>52.4</v>
       </c>
       <c r="J11" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K11" t="n">
-        <v>753.4744118316256</v>
+        <v>496.272758163412</v>
       </c>
       <c r="L11" t="n">
-        <v>1401.924411831626</v>
+        <v>726.7700404749698</v>
       </c>
       <c r="M11" t="n">
-        <v>1585.241587554807</v>
+        <v>726.7700404749698</v>
       </c>
       <c r="N11" t="n">
-        <v>2233.691587554807</v>
+        <v>726.7700404749698</v>
       </c>
       <c r="O11" t="n">
-        <v>2410.244759641279</v>
+        <v>1375.22004047497</v>
       </c>
       <c r="P11" t="n">
-        <v>2620</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q11" t="n">
         <v>2620</v>
@@ -5087,25 +5087,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>502.743697048149</v>
+        <v>1016.832194327384</v>
       </c>
       <c r="C12" t="n">
-        <v>460.2185329617658</v>
+        <v>974.3070302410013</v>
       </c>
       <c r="D12" t="n">
-        <v>430.9885461964096</v>
+        <v>945.077043475645</v>
       </c>
       <c r="E12" t="n">
-        <v>407.0773368813464</v>
+        <v>598.9436119383595</v>
       </c>
       <c r="F12" t="n">
-        <v>386.2326476511677</v>
+        <v>255.8767004859585</v>
       </c>
       <c r="G12" t="n">
-        <v>380.2224055818624</v>
+        <v>249.8664584166532</v>
       </c>
       <c r="H12" t="n">
-        <v>52.4</v>
+        <v>244.266275057013</v>
       </c>
       <c r="I12" t="n">
         <v>52.4</v>
@@ -5138,25 +5138,25 @@
         <v>2132.917892265885</v>
       </c>
       <c r="S12" t="n">
-        <v>1773.479928583419</v>
+        <v>1676.451921270565</v>
       </c>
       <c r="T12" t="n">
-        <v>1689.463823065442</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U12" t="n">
-        <v>1285.26339296653</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V12" t="n">
-        <v>1188.787971560954</v>
+        <v>1380.654246617967</v>
       </c>
       <c r="W12" t="n">
-        <v>1074.26964538941</v>
+        <v>1266.135920446423</v>
       </c>
       <c r="X12" t="n">
-        <v>972.3880903940692</v>
+        <v>1164.254365451082</v>
       </c>
       <c r="Y12" t="n">
-        <v>891.1846633575699</v>
+        <v>1083.050938414583</v>
       </c>
     </row>
     <row r="13">
@@ -5166,31 +5166,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>673.4417775581344</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C13" t="n">
-        <v>719.2537833765701</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D13" t="n">
-        <v>752.3829275015702</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E13" t="n">
-        <v>790.0218317129832</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F13" t="n">
-        <v>834.1928043049187</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G13" t="n">
-        <v>908.0645554377056</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H13" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I13" t="n">
-        <v>1163.862419205317</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J13" t="n">
-        <v>1491.077756743014</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K13" t="n">
         <v>1597.372803794637</v>
@@ -5199,7 +5199,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M13" t="n">
-        <v>1492.275360291075</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N13" t="n">
         <v>1339.839881046618</v>
@@ -5214,7 +5214,7 @@
         <v>463.3441798078979</v>
       </c>
       <c r="R13" t="n">
-        <v>81.68251716755645</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S13" t="n">
         <v>52.4</v>
@@ -5223,19 +5223,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U13" t="n">
-        <v>329.4820370429931</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V13" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W13" t="n">
-        <v>539.8143481886165</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X13" t="n">
-        <v>610.65513921281</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y13" t="n">
-        <v>641.8744398918423</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="14">
@@ -5260,7 +5260,7 @@
         <v>210.4665309010492</v>
       </c>
       <c r="G14" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H14" t="n">
         <v>52.4</v>
@@ -5269,25 +5269,25 @@
         <v>52.4</v>
       </c>
       <c r="J14" t="n">
-        <v>567.6776741934345</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K14" t="n">
-        <v>1216.127674193434</v>
+        <v>790.1259849731395</v>
       </c>
       <c r="L14" t="n">
-        <v>1446.624956504992</v>
+        <v>1020.623267284697</v>
       </c>
       <c r="M14" t="n">
-        <v>1446.624956504992</v>
+        <v>1669.073267284698</v>
       </c>
       <c r="N14" t="n">
-        <v>1637.361628029778</v>
+        <v>1669.073267284698</v>
       </c>
       <c r="O14" t="n">
-        <v>1813.91480011625</v>
+        <v>1845.626439371171</v>
       </c>
       <c r="P14" t="n">
-        <v>2023.670040474971</v>
+        <v>2055.381679729891</v>
       </c>
       <c r="Q14" t="n">
         <v>2620</v>
@@ -5324,22 +5324,22 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>824.9659192703712</v>
+        <v>1372.382356401963</v>
       </c>
       <c r="C15" t="n">
-        <v>460.2185329617658</v>
+        <v>1007.634970093357</v>
       </c>
       <c r="D15" t="n">
-        <v>108.7663239741874</v>
+        <v>753.2107684186319</v>
       </c>
       <c r="E15" t="n">
-        <v>84.85511465912413</v>
+        <v>729.2995591035686</v>
       </c>
       <c r="F15" t="n">
-        <v>64.01042542894548</v>
+        <v>708.45486987339</v>
       </c>
       <c r="G15" t="n">
-        <v>58.00018335964018</v>
+        <v>380.2224055818624</v>
       </c>
       <c r="H15" t="n">
         <v>52.4</v>
@@ -5393,7 +5393,7 @@
         <v>1519.804527525661</v>
       </c>
       <c r="Y15" t="n">
-        <v>1213.406885579792</v>
+        <v>1438.601100489161</v>
       </c>
     </row>
     <row r="16">
@@ -5418,40 +5418,40 @@
         <v>834.1928043049187</v>
       </c>
       <c r="G16" t="n">
-        <v>908.0645554377063</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H16" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I16" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J16" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K16" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L16" t="n">
         <v>1591.155096928856</v>
       </c>
       <c r="M16" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N16" t="n">
-        <v>1339.839881046619</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O16" t="n">
-        <v>1109.635154952565</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P16" t="n">
-        <v>818.3161660963816</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q16" t="n">
-        <v>463.3441798078988</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R16" t="n">
-        <v>81.68251716755736</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S16" t="n">
         <v>52.4</v>
@@ -5497,7 +5497,7 @@
         <v>210.4665309010492</v>
       </c>
       <c r="G17" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H17" t="n">
         <v>52.4</v>
@@ -5518,13 +5518,13 @@
         <v>1624.372722611331</v>
       </c>
       <c r="N17" t="n">
-        <v>1637.361628029778</v>
+        <v>2233.691587554807</v>
       </c>
       <c r="O17" t="n">
-        <v>1813.91480011625</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P17" t="n">
-        <v>2023.670040474971</v>
+        <v>2620</v>
       </c>
       <c r="Q17" t="n">
         <v>2620</v>
@@ -5561,10 +5561,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>824.9659192703712</v>
+        <v>180.5214748259267</v>
       </c>
       <c r="C18" t="n">
-        <v>460.2185329617658</v>
+        <v>137.9963107395436</v>
       </c>
       <c r="D18" t="n">
         <v>108.7663239741874</v>
@@ -5609,28 +5609,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R18" t="n">
-        <v>2132.917892265885</v>
+        <v>1810.695670043663</v>
       </c>
       <c r="S18" t="n">
-        <v>1998.674143492788</v>
+        <v>1354.229699048343</v>
       </c>
       <c r="T18" t="n">
-        <v>1914.658037974811</v>
+        <v>947.9913713081444</v>
       </c>
       <c r="U18" t="n">
-        <v>1832.679830098122</v>
+        <v>866.0131634314549</v>
       </c>
       <c r="V18" t="n">
-        <v>1736.204408692546</v>
+        <v>769.537742025879</v>
       </c>
       <c r="W18" t="n">
-        <v>1621.686082521002</v>
+        <v>655.019415854335</v>
       </c>
       <c r="X18" t="n">
-        <v>1519.804527525661</v>
+        <v>553.137860858994</v>
       </c>
       <c r="Y18" t="n">
-        <v>1213.406885579792</v>
+        <v>246.7402189131253</v>
       </c>
     </row>
     <row r="19">
@@ -5664,31 +5664,31 @@
         <v>1163.862419205318</v>
       </c>
       <c r="J19" t="n">
-        <v>1491.077756743016</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K19" t="n">
-        <v>1597.372803794638</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L19" t="n">
-        <v>1591.155096928857</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M19" t="n">
-        <v>1492.275360291077</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N19" t="n">
-        <v>1339.83988104662</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O19" t="n">
-        <v>1109.635154952566</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P19" t="n">
-        <v>818.3161660963821</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q19" t="n">
-        <v>463.3441798078993</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R19" t="n">
-        <v>81.68251716755788</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S19" t="n">
         <v>52.4</v>
@@ -5719,22 +5719,22 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>608.2066695820786</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C20" t="n">
-        <v>476.4141663063272</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D20" t="n">
-        <v>384.1523928317314</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E20" t="n">
-        <v>297.9268477742883</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F20" t="n">
-        <v>211.1696470591248</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G20" t="n">
-        <v>127.0464193797368</v>
+        <v>126.3433032216612</v>
       </c>
       <c r="H20" t="n">
         <v>52.4</v>
@@ -5746,49 +5746,49 @@
         <v>141.6759849731395</v>
       </c>
       <c r="K20" t="n">
-        <v>790.1259849731395</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L20" t="n">
-        <v>1438.575984973139</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M20" t="n">
-        <v>2087.025984973143</v>
+        <v>1206.420004922889</v>
       </c>
       <c r="N20" t="n">
-        <v>2233.69158755488</v>
+        <v>1854.870004922889</v>
       </c>
       <c r="O20" t="n">
-        <v>2410.244759641353</v>
+        <v>2410.244759641279</v>
       </c>
       <c r="P20" t="n">
-        <v>2620.000000000073</v>
+        <v>2620</v>
       </c>
       <c r="Q20" t="n">
-        <v>2620.000000000073</v>
+        <v>2620</v>
       </c>
       <c r="R20" t="n">
         <v>2620</v>
       </c>
       <c r="S20" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T20" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U20" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V20" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W20" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X20" t="n">
-        <v>967.1124732572108</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y20" t="n">
-        <v>772.852440244275</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="21">
@@ -5801,19 +5801,19 @@
         <v>502.743697048149</v>
       </c>
       <c r="C21" t="n">
-        <v>137.9963107395436</v>
+        <v>460.2185329617659</v>
       </c>
       <c r="D21" t="n">
-        <v>108.7663239741874</v>
+        <v>430.9885461964097</v>
       </c>
       <c r="E21" t="n">
-        <v>84.85511465912413</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F21" t="n">
         <v>64.01042542894548</v>
       </c>
       <c r="G21" t="n">
-        <v>58.00018335964016</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H21" t="n">
         <v>52.4</v>
@@ -5852,22 +5852,22 @@
         <v>1998.674143492788</v>
       </c>
       <c r="T21" t="n">
-        <v>1914.658037974811</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U21" t="n">
-        <v>1832.679830098122</v>
+        <v>1285.26339296653</v>
       </c>
       <c r="V21" t="n">
-        <v>1736.204408692546</v>
+        <v>1188.787971560954</v>
       </c>
       <c r="W21" t="n">
-        <v>1621.686082521002</v>
+        <v>1074.26964538941</v>
       </c>
       <c r="X21" t="n">
-        <v>1294.610312616292</v>
+        <v>972.3880903940692</v>
       </c>
       <c r="Y21" t="n">
-        <v>891.1846633575699</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="22">
@@ -5877,31 +5877,31 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>673.4417775581345</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C22" t="n">
-        <v>719.2537833765703</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D22" t="n">
-        <v>752.3829275015703</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E22" t="n">
-        <v>790.0218317129833</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F22" t="n">
-        <v>834.1928043049188</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G22" t="n">
-        <v>908.0645554377057</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H22" t="n">
         <v>1003.21633305612</v>
       </c>
       <c r="I22" t="n">
-        <v>1163.862419205318</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J22" t="n">
-        <v>1491.077756743015</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K22" t="n">
         <v>1597.372803794637</v>
@@ -5910,7 +5910,7 @@
         <v>1591.155096928856</v>
       </c>
       <c r="M22" t="n">
-        <v>1492.275360291076</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N22" t="n">
         <v>1339.839881046618</v>
@@ -5925,7 +5925,7 @@
         <v>463.3441798078979</v>
       </c>
       <c r="R22" t="n">
-        <v>81.68251716755651</v>
+        <v>81.68251716755645</v>
       </c>
       <c r="S22" t="n">
         <v>52.4</v>
@@ -5934,19 +5934,19 @@
         <v>163.0851070276573</v>
       </c>
       <c r="U22" t="n">
-        <v>329.4820370429932</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V22" t="n">
         <v>448.1134299289391</v>
       </c>
       <c r="W22" t="n">
-        <v>539.8143481886166</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X22" t="n">
-        <v>610.6551392128101</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y22" t="n">
-        <v>641.8744398918424</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="23">
@@ -5980,22 +5980,22 @@
         <v>52.4</v>
       </c>
       <c r="J23" t="n">
-        <v>141.6759849731395</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K23" t="n">
-        <v>790.1259849731395</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L23" t="n">
-        <v>1438.575984973139</v>
+        <v>1401.924411831626</v>
       </c>
       <c r="M23" t="n">
-        <v>1438.575984973139</v>
+        <v>1794.996827913527</v>
       </c>
       <c r="N23" t="n">
-        <v>1794.996827913518</v>
+        <v>1794.996827913527</v>
       </c>
       <c r="O23" t="n">
-        <v>1971.549999999991</v>
+        <v>1971.549999999999</v>
       </c>
       <c r="P23" t="n">
         <v>2620</v>
@@ -6007,19 +6007,19 @@
         <v>2620</v>
       </c>
       <c r="S23" t="n">
-        <v>2477.038452472668</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T23" t="n">
-        <v>2213.182776293874</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U23" t="n">
-        <v>1879.745133467756</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V23" t="n">
-        <v>1565.754199965913</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W23" t="n">
-        <v>1243.154729278087</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X23" t="n">
         <v>967.1124732572108</v>
@@ -6035,16 +6035,16 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1372.382356401963</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C24" t="n">
-        <v>1104.66297740621</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D24" t="n">
-        <v>753.2107684186319</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E24" t="n">
-        <v>407.0773368813464</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F24" t="n">
         <v>64.01042542894548</v>
@@ -6083,28 +6083,28 @@
         <v>2313.990605368536</v>
       </c>
       <c r="R24" t="n">
-        <v>2132.917892265885</v>
+        <v>1810.695670043663</v>
       </c>
       <c r="S24" t="n">
-        <v>1998.674143492788</v>
+        <v>1676.451921270566</v>
       </c>
       <c r="T24" t="n">
-        <v>1914.658037974811</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U24" t="n">
-        <v>1832.679830098122</v>
+        <v>1188.235385653677</v>
       </c>
       <c r="V24" t="n">
-        <v>1736.204408692546</v>
+        <v>866.5657493387318</v>
       </c>
       <c r="W24" t="n">
-        <v>1621.686082521002</v>
+        <v>752.0474231671878</v>
       </c>
       <c r="X24" t="n">
-        <v>1519.804527525661</v>
+        <v>650.1658681718469</v>
       </c>
       <c r="Y24" t="n">
-        <v>1438.601100489161</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="25">
@@ -6144,25 +6144,25 @@
         <v>1597.372803794637</v>
       </c>
       <c r="L25" t="n">
-        <v>1594.034249936398</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M25" t="n">
-        <v>1495.154513298618</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N25" t="n">
-        <v>1342.71903405416</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O25" t="n">
-        <v>1112.514307960106</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P25" t="n">
-        <v>821.1953191039224</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q25" t="n">
-        <v>466.2233328154396</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R25" t="n">
-        <v>84.56167017509824</v>
+        <v>81.68251716755651</v>
       </c>
       <c r="S25" t="n">
         <v>52.4</v>
@@ -6193,76 +6193,76 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>608.2066695820878</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C26" t="n">
-        <v>476.4141663063364</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D26" t="n">
-        <v>384.1523928317406</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E26" t="n">
-        <v>297.9268477742975</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F26" t="n">
-        <v>211.169647059134</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G26" t="n">
-        <v>127.046419379746</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H26" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="I26" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="J26" t="n">
-        <v>567.6776741934437</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K26" t="n">
-        <v>753.4744118316348</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L26" t="n">
-        <v>983.9716941431925</v>
+        <v>983.9716941431833</v>
       </c>
       <c r="M26" t="n">
-        <v>1632.421694143209</v>
+        <v>983.9716941431834</v>
       </c>
       <c r="N26" t="n">
-        <v>1637.361628030236</v>
+        <v>983.9716941431834</v>
       </c>
       <c r="O26" t="n">
-        <v>1813.914800116709</v>
+        <v>1632.421694143184</v>
       </c>
       <c r="P26" t="n">
-        <v>2023.670040475429</v>
+        <v>2023.670040474971</v>
       </c>
       <c r="Q26" t="n">
-        <v>2620.000000000458</v>
+        <v>2620</v>
       </c>
       <c r="R26" t="n">
-        <v>2620.000000000458</v>
+        <v>2620</v>
       </c>
       <c r="S26" t="n">
-        <v>2477.038452472677</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T26" t="n">
-        <v>2213.182776293883</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U26" t="n">
-        <v>1879.745133467765</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V26" t="n">
-        <v>1565.754199965922</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W26" t="n">
-        <v>1243.154729278097</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X26" t="n">
-        <v>967.11247325722</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y26" t="n">
-        <v>772.8524402442843</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="27">
@@ -6272,76 +6272,76 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>824.9659192703805</v>
+        <v>727.9379119575183</v>
       </c>
       <c r="C27" t="n">
-        <v>460.2185329617751</v>
+        <v>685.4127478711351</v>
       </c>
       <c r="D27" t="n">
-        <v>430.9885461964188</v>
+        <v>656.1827611057789</v>
       </c>
       <c r="E27" t="n">
-        <v>407.0773368813556</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F27" t="n">
-        <v>64.01042542895465</v>
+        <v>386.2326476511677</v>
       </c>
       <c r="G27" t="n">
-        <v>58.00018335964935</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H27" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="I27" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="J27" t="n">
-        <v>250.1913459300251</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K27" t="n">
-        <v>565.5796394772387</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L27" t="n">
-        <v>1006.615493996967</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M27" t="n">
-        <v>1290.710885739826</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N27" t="n">
-        <v>1627.246884215319</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O27" t="n">
-        <v>2052.228604861302</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P27" t="n">
-        <v>2313.990605368545</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q27" t="n">
-        <v>2313.990605368545</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R27" t="n">
-        <v>2132.917892265894</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S27" t="n">
-        <v>1998.674143492797</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T27" t="n">
-        <v>1914.65803797482</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U27" t="n">
-        <v>1832.679830098131</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V27" t="n">
-        <v>1736.204408692555</v>
+        <v>1413.982186470324</v>
       </c>
       <c r="W27" t="n">
-        <v>1396.491867611642</v>
+        <v>1299.46386029878</v>
       </c>
       <c r="X27" t="n">
-        <v>1294.610312616301</v>
+        <v>1197.582305303438</v>
       </c>
       <c r="Y27" t="n">
-        <v>1213.406885579801</v>
+        <v>1116.378878266939</v>
       </c>
     </row>
     <row r="28">
@@ -6351,76 +6351,76 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>673.4417775581436</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C28" t="n">
-        <v>719.2537833765793</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D28" t="n">
-        <v>752.3829275015794</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E28" t="n">
-        <v>790.0218317129924</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F28" t="n">
-        <v>834.1928043049279</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G28" t="n">
-        <v>908.0645554377148</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H28" t="n">
-        <v>1003.216333056129</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I28" t="n">
-        <v>1163.862419205327</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J28" t="n">
-        <v>1491.077756743024</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K28" t="n">
-        <v>1597.372803794646</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L28" t="n">
-        <v>1594.034249936407</v>
+        <v>1594.034249936398</v>
       </c>
       <c r="M28" t="n">
-        <v>1495.154513298627</v>
+        <v>1495.154513298618</v>
       </c>
       <c r="N28" t="n">
-        <v>1342.719034054169</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O28" t="n">
-        <v>1112.514307960115</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P28" t="n">
-        <v>821.1953191039316</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q28" t="n">
-        <v>466.2233328154488</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R28" t="n">
-        <v>84.56167017510739</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S28" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="T28" t="n">
-        <v>163.0851070276665</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U28" t="n">
-        <v>329.4820370430023</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V28" t="n">
-        <v>448.1134299289482</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W28" t="n">
-        <v>539.8143481886257</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X28" t="n">
-        <v>610.6551392128192</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y28" t="n">
-        <v>641.8744398918515</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="29">
@@ -6430,76 +6430,76 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>607.5035534244613</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C29" t="n">
-        <v>475.7110501487099</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D29" t="n">
-        <v>383.4492766741141</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E29" t="n">
-        <v>297.223731616671</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F29" t="n">
-        <v>210.4665309015076</v>
+        <v>210.4665309010492</v>
       </c>
       <c r="G29" t="n">
-        <v>126.3433032221196</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H29" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="I29" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="J29" t="n">
-        <v>567.6776741934437</v>
+        <v>567.6776741934345</v>
       </c>
       <c r="K29" t="n">
-        <v>1216.127674193557</v>
+        <v>753.4744118316256</v>
       </c>
       <c r="L29" t="n">
-        <v>1446.624956505115</v>
+        <v>1401.924411831626</v>
       </c>
       <c r="M29" t="n">
-        <v>2095.074956505142</v>
+        <v>1401.924411831626</v>
       </c>
       <c r="N29" t="n">
-        <v>2095.074956505142</v>
+        <v>1401.924411831626</v>
       </c>
       <c r="O29" t="n">
-        <v>2271.628128591615</v>
+        <v>1578.477583918098</v>
       </c>
       <c r="P29" t="n">
-        <v>2620.000000000458</v>
+        <v>2226.927583918101</v>
       </c>
       <c r="Q29" t="n">
-        <v>2620.000000000458</v>
+        <v>2620</v>
       </c>
       <c r="R29" t="n">
-        <v>2620.000000000458</v>
+        <v>2620</v>
       </c>
       <c r="S29" t="n">
-        <v>2476.33533631505</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T29" t="n">
-        <v>2212.479660136256</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U29" t="n">
-        <v>1879.042017310138</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V29" t="n">
-        <v>1565.051083808296</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W29" t="n">
-        <v>1242.45161312047</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X29" t="n">
-        <v>966.4093570995935</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y29" t="n">
-        <v>772.1493240866578</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="30">
@@ -6509,76 +6509,76 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>502.7436970481582</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C30" t="n">
-        <v>460.2185329617751</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D30" t="n">
-        <v>430.9885461964188</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E30" t="n">
-        <v>407.0773368813556</v>
+        <v>84.85511465912413</v>
       </c>
       <c r="F30" t="n">
-        <v>64.01042542895465</v>
+        <v>64.01042542894548</v>
       </c>
       <c r="G30" t="n">
-        <v>58.00018335964935</v>
+        <v>58.00018335964016</v>
       </c>
       <c r="H30" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="I30" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="J30" t="n">
-        <v>250.1913459300251</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K30" t="n">
-        <v>565.5796394772387</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L30" t="n">
-        <v>1006.615493996967</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M30" t="n">
-        <v>1290.710885739826</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N30" t="n">
-        <v>1627.246884215319</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O30" t="n">
-        <v>2052.228604861302</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P30" t="n">
-        <v>2313.990605368545</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q30" t="n">
-        <v>2313.990605368545</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R30" t="n">
-        <v>2132.917892265894</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S30" t="n">
-        <v>1773.479928583428</v>
+        <v>1676.451921270565</v>
       </c>
       <c r="T30" t="n">
-        <v>1689.463823065451</v>
+        <v>1592.435815752589</v>
       </c>
       <c r="U30" t="n">
-        <v>1607.485615188762</v>
+        <v>1510.457607875899</v>
       </c>
       <c r="V30" t="n">
-        <v>1188.787971560963</v>
+        <v>1413.982186470323</v>
       </c>
       <c r="W30" t="n">
-        <v>752.0474231671971</v>
+        <v>1299.463860298779</v>
       </c>
       <c r="X30" t="n">
-        <v>650.1658681718561</v>
+        <v>875.3600830812161</v>
       </c>
       <c r="Y30" t="n">
-        <v>568.9624411353568</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="31">
@@ -6588,76 +6588,76 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>673.4417775581436</v>
+        <v>673.4417775581345</v>
       </c>
       <c r="C31" t="n">
-        <v>719.2537833765793</v>
+        <v>719.2537833765703</v>
       </c>
       <c r="D31" t="n">
-        <v>752.3829275015794</v>
+        <v>752.3829275015703</v>
       </c>
       <c r="E31" t="n">
-        <v>790.0218317129924</v>
+        <v>790.0218317129833</v>
       </c>
       <c r="F31" t="n">
-        <v>834.1928043049279</v>
+        <v>834.1928043049188</v>
       </c>
       <c r="G31" t="n">
-        <v>908.0645554377148</v>
+        <v>908.0645554377057</v>
       </c>
       <c r="H31" t="n">
-        <v>1003.216333056129</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I31" t="n">
-        <v>1163.862419205327</v>
+        <v>1163.862419205318</v>
       </c>
       <c r="J31" t="n">
-        <v>1491.077756743024</v>
+        <v>1491.077756743015</v>
       </c>
       <c r="K31" t="n">
-        <v>1597.372803794646</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L31" t="n">
-        <v>1591.155096928865</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M31" t="n">
-        <v>1492.275360291085</v>
+        <v>1492.275360291076</v>
       </c>
       <c r="N31" t="n">
-        <v>1342.719034054169</v>
+        <v>1342.71903405416</v>
       </c>
       <c r="O31" t="n">
-        <v>1112.514307960115</v>
+        <v>1112.514307960106</v>
       </c>
       <c r="P31" t="n">
-        <v>821.1953191039316</v>
+        <v>821.1953191039224</v>
       </c>
       <c r="Q31" t="n">
-        <v>466.2233328154488</v>
+        <v>466.2233328154396</v>
       </c>
       <c r="R31" t="n">
-        <v>84.56167017510739</v>
+        <v>84.56167017509824</v>
       </c>
       <c r="S31" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="T31" t="n">
-        <v>163.0851070276665</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U31" t="n">
-        <v>329.4820370430023</v>
+        <v>329.4820370429932</v>
       </c>
       <c r="V31" t="n">
-        <v>448.1134299289482</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W31" t="n">
-        <v>539.8143481886257</v>
+        <v>539.8143481886166</v>
       </c>
       <c r="X31" t="n">
-        <v>610.6551392128192</v>
+        <v>610.6551392128101</v>
       </c>
       <c r="Y31" t="n">
-        <v>641.8744398918515</v>
+        <v>641.8744398918424</v>
       </c>
     </row>
     <row r="32">
@@ -6667,76 +6667,76 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>607.5035534244613</v>
+        <v>607.5035534240029</v>
       </c>
       <c r="C32" t="n">
-        <v>475.7110501487099</v>
+        <v>475.7110501482515</v>
       </c>
       <c r="D32" t="n">
-        <v>383.4492766741141</v>
+        <v>383.4492766736557</v>
       </c>
       <c r="E32" t="n">
-        <v>297.223731616671</v>
+        <v>297.2237316162127</v>
       </c>
       <c r="F32" t="n">
-        <v>210.4665309015076</v>
+        <v>211.1696470591248</v>
       </c>
       <c r="G32" t="n">
-        <v>127.046419379746</v>
+        <v>127.0464193797368</v>
       </c>
       <c r="H32" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="I32" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="J32" t="n">
-        <v>141.6759849731487</v>
+        <v>141.6759849731395</v>
       </c>
       <c r="K32" t="n">
-        <v>790.125984973262</v>
+        <v>327.4727226113304</v>
       </c>
       <c r="L32" t="n">
-        <v>1020.62326728482</v>
+        <v>557.9700049228883</v>
       </c>
       <c r="M32" t="n">
-        <v>1669.073267284859</v>
+        <v>1206.420004922892</v>
       </c>
       <c r="N32" t="n">
-        <v>1794.996827913946</v>
+        <v>1206.420004922892</v>
       </c>
       <c r="O32" t="n">
-        <v>1971.550000000419</v>
+        <v>1854.870004922896</v>
       </c>
       <c r="P32" t="n">
-        <v>2620.000000000458</v>
+        <v>2064.625245281616</v>
       </c>
       <c r="Q32" t="n">
-        <v>2620.000000000458</v>
+        <v>2620</v>
       </c>
       <c r="R32" t="n">
-        <v>2620.000000000458</v>
+        <v>2620</v>
       </c>
       <c r="S32" t="n">
-        <v>2476.33533631505</v>
+        <v>2476.335336314592</v>
       </c>
       <c r="T32" t="n">
-        <v>2212.479660136256</v>
+        <v>2212.479660135798</v>
       </c>
       <c r="U32" t="n">
-        <v>1879.042017310138</v>
+        <v>1879.04201730968</v>
       </c>
       <c r="V32" t="n">
-        <v>1565.051083808296</v>
+        <v>1565.051083807838</v>
       </c>
       <c r="W32" t="n">
-        <v>1242.45161312047</v>
+        <v>1242.451613120012</v>
       </c>
       <c r="X32" t="n">
-        <v>966.4093570995935</v>
+        <v>966.4093570991351</v>
       </c>
       <c r="Y32" t="n">
-        <v>772.1493240866578</v>
+        <v>772.1493240861994</v>
       </c>
     </row>
     <row r="33">
@@ -6746,76 +6746,76 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>727.9379119575274</v>
+        <v>502.743697048149</v>
       </c>
       <c r="C33" t="n">
-        <v>685.4127478711442</v>
+        <v>460.2185329617658</v>
       </c>
       <c r="D33" t="n">
-        <v>656.182761105788</v>
+        <v>430.9885461964096</v>
       </c>
       <c r="E33" t="n">
-        <v>310.0493295685025</v>
+        <v>407.0773368813464</v>
       </c>
       <c r="F33" t="n">
-        <v>64.01042542895465</v>
+        <v>386.2326476511677</v>
       </c>
       <c r="G33" t="n">
-        <v>58.00018335964935</v>
+        <v>58.00018335964018</v>
       </c>
       <c r="H33" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="I33" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="J33" t="n">
-        <v>250.1913459300251</v>
+        <v>250.191345930016</v>
       </c>
       <c r="K33" t="n">
-        <v>565.5796394772387</v>
+        <v>565.5796394772295</v>
       </c>
       <c r="L33" t="n">
-        <v>1006.615493996967</v>
+        <v>1006.615493996958</v>
       </c>
       <c r="M33" t="n">
-        <v>1290.710885739826</v>
+        <v>1290.710885739817</v>
       </c>
       <c r="N33" t="n">
-        <v>1627.246884215319</v>
+        <v>1627.24688421531</v>
       </c>
       <c r="O33" t="n">
-        <v>2052.228604861302</v>
+        <v>2052.228604861293</v>
       </c>
       <c r="P33" t="n">
-        <v>2313.990605368545</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="Q33" t="n">
-        <v>2313.990605368545</v>
+        <v>2313.990605368536</v>
       </c>
       <c r="R33" t="n">
-        <v>2132.917892265894</v>
+        <v>2132.917892265885</v>
       </c>
       <c r="S33" t="n">
-        <v>1998.674143492797</v>
+        <v>1998.674143492788</v>
       </c>
       <c r="T33" t="n">
-        <v>1914.65803797482</v>
+        <v>1689.463823065442</v>
       </c>
       <c r="U33" t="n">
-        <v>1832.679830098131</v>
+        <v>1607.485615188752</v>
       </c>
       <c r="V33" t="n">
-        <v>1736.204408692555</v>
+        <v>1511.010193783176</v>
       </c>
       <c r="W33" t="n">
-        <v>1621.686082521011</v>
+        <v>1396.491867611632</v>
       </c>
       <c r="X33" t="n">
-        <v>1197.582305303448</v>
+        <v>972.3880903940692</v>
       </c>
       <c r="Y33" t="n">
-        <v>794.156656044726</v>
+        <v>568.9624411353476</v>
       </c>
     </row>
     <row r="34">
@@ -6825,76 +6825,76 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>673.4417775581436</v>
+        <v>673.4417775581344</v>
       </c>
       <c r="C34" t="n">
-        <v>719.2537833765793</v>
+        <v>719.2537833765701</v>
       </c>
       <c r="D34" t="n">
-        <v>752.3829275015794</v>
+        <v>752.3829275015702</v>
       </c>
       <c r="E34" t="n">
-        <v>790.0218317129924</v>
+        <v>790.0218317129832</v>
       </c>
       <c r="F34" t="n">
-        <v>834.1928043049279</v>
+        <v>834.1928043049187</v>
       </c>
       <c r="G34" t="n">
-        <v>908.0645554377148</v>
+        <v>908.0645554377056</v>
       </c>
       <c r="H34" t="n">
-        <v>1003.216333056129</v>
+        <v>1003.21633305612</v>
       </c>
       <c r="I34" t="n">
-        <v>1163.862419205327</v>
+        <v>1163.862419205317</v>
       </c>
       <c r="J34" t="n">
-        <v>1491.077756743024</v>
+        <v>1491.077756743014</v>
       </c>
       <c r="K34" t="n">
-        <v>1597.372803794646</v>
+        <v>1597.372803794637</v>
       </c>
       <c r="L34" t="n">
-        <v>1591.155096928865</v>
+        <v>1591.155096928856</v>
       </c>
       <c r="M34" t="n">
-        <v>1492.275360291085</v>
+        <v>1492.275360291075</v>
       </c>
       <c r="N34" t="n">
-        <v>1339.839881046628</v>
+        <v>1339.839881046618</v>
       </c>
       <c r="O34" t="n">
-        <v>1109.635154952574</v>
+        <v>1109.635154952564</v>
       </c>
       <c r="P34" t="n">
-        <v>821.1953191039316</v>
+        <v>818.3161660963807</v>
       </c>
       <c r="Q34" t="n">
-        <v>466.2233328154488</v>
+        <v>463.3441798078979</v>
       </c>
       <c r="R34" t="n">
-        <v>84.56167017510739</v>
+        <v>84.56167017509823</v>
       </c>
       <c r="S34" t="n">
-        <v>52.40000000000917</v>
+        <v>52.4</v>
       </c>
       <c r="T34" t="n">
-        <v>163.0851070276665</v>
+        <v>163.0851070276573</v>
       </c>
       <c r="U34" t="n">
-        <v>329.4820370430023</v>
+        <v>329.4820370429931</v>
       </c>
       <c r="V34" t="n">
-        <v>448.1134299289482</v>
+        <v>448.1134299289391</v>
       </c>
       <c r="W34" t="n">
-        <v>539.8143481886257</v>
+        <v>539.8143481886165</v>
       </c>
       <c r="X34" t="n">
-        <v>610.6551392128192</v>
+        <v>610.65513921281</v>
       </c>
       <c r="Y34" t="n">
-        <v>641.8744398918515</v>
+        <v>641.8744398918423</v>
       </c>
     </row>
     <row r="35">
@@ -6904,76 +6904,76 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>113.8065837273388</v>
+        <v>117.1408562629478</v>
       </c>
       <c r="C35" t="n">
-        <v>60.8019592394662</v>
+        <v>64.13623177507512</v>
       </c>
       <c r="D35" t="n">
-        <v>47.32806455274924</v>
+        <v>50.66233708835816</v>
       </c>
       <c r="E35" t="n">
-        <v>39.89039828318495</v>
+        <v>43.22467081879388</v>
       </c>
       <c r="F35" t="n">
-        <v>35.25534889151837</v>
+        <v>35.25534889150917</v>
       </c>
       <c r="G35" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="H35" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="I35" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J35" t="n">
-        <v>119.1959849731487</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K35" t="n">
-        <v>304.9927226113396</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L35" t="n">
-        <v>535.4900049228974</v>
+        <v>545.7247596412399</v>
       </c>
       <c r="M35" t="n">
-        <v>905.7500049229695</v>
+        <v>915.9847596412598</v>
       </c>
       <c r="N35" t="n">
-        <v>1109.691587555113</v>
+        <v>915.9847596412598</v>
       </c>
       <c r="O35" t="n">
-        <v>1286.244759641585</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P35" t="n">
-        <v>1496.000000000306</v>
+        <v>1496</v>
       </c>
       <c r="Q35" t="n">
-        <v>1496.000000000306</v>
+        <v>1496</v>
       </c>
       <c r="R35" t="n">
-        <v>1496.000000000306</v>
+        <v>1496</v>
       </c>
       <c r="S35" t="n">
-        <v>1431.123215102776</v>
+        <v>1434.457487638385</v>
       </c>
       <c r="T35" t="n">
-        <v>1246.055417711861</v>
+        <v>1249.38969024747</v>
       </c>
       <c r="U35" t="n">
-        <v>991.4056536736218</v>
+        <v>994.7399262092307</v>
       </c>
       <c r="V35" t="n">
-        <v>756.2025989596583</v>
+        <v>759.5368714952672</v>
       </c>
       <c r="W35" t="n">
-        <v>512.3910070597112</v>
+        <v>515.7252795953201</v>
       </c>
       <c r="X35" t="n">
-        <v>315.1366298267135</v>
+        <v>318.4709023623224</v>
       </c>
       <c r="Y35" t="n">
-        <v>199.6644756016565</v>
+        <v>202.9987481372655</v>
       </c>
     </row>
     <row r="36">
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>916.3053954970014</v>
+        <v>29.92</v>
       </c>
       <c r="C36" t="n">
-        <v>916.3053954970014</v>
+        <v>29.92</v>
       </c>
       <c r="D36" t="n">
-        <v>564.853186509423</v>
+        <v>29.92</v>
       </c>
       <c r="E36" t="n">
-        <v>564.853186509423</v>
+        <v>29.92</v>
       </c>
       <c r="F36" t="n">
-        <v>221.7862750570222</v>
+        <v>29.92</v>
       </c>
       <c r="G36" t="n">
-        <v>221.7862750570222</v>
+        <v>29.92</v>
       </c>
       <c r="H36" t="n">
-        <v>221.7862750570222</v>
+        <v>29.92</v>
       </c>
       <c r="I36" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J36" t="n">
-        <v>227.7113459300251</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K36" t="n">
-        <v>543.0996394772387</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L36" t="n">
-        <v>913.3596394773108</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M36" t="n">
-        <v>1068.534465906626</v>
+        <v>884.0224426446173</v>
       </c>
       <c r="N36" t="n">
-        <v>1405.070464382119</v>
+        <v>884.0224426446173</v>
       </c>
       <c r="O36" t="n">
-        <v>1451.197204215207</v>
+        <v>1234.237999492757</v>
       </c>
       <c r="P36" t="n">
-        <v>1496.000000000306</v>
+        <v>1496</v>
       </c>
       <c r="Q36" t="n">
-        <v>1422.956031069576</v>
+        <v>1496</v>
       </c>
       <c r="R36" t="n">
-        <v>1059.107035758573</v>
+        <v>1393.715165685228</v>
       </c>
       <c r="S36" t="n">
-        <v>1003.651165773355</v>
+        <v>1338.259295700009</v>
       </c>
       <c r="T36" t="n">
-        <v>998.4229390432571</v>
+        <v>1333.031068969912</v>
       </c>
       <c r="U36" t="n">
-        <v>995.2326099544464</v>
+        <v>1329.840739881101</v>
       </c>
       <c r="V36" t="n">
-        <v>977.5450673367493</v>
+        <v>952.0629621033031</v>
       </c>
       <c r="W36" t="n">
-        <v>941.8146199530842</v>
+        <v>574.285184325505</v>
       </c>
       <c r="X36" t="n">
-        <v>918.720943745622</v>
+        <v>407.6977777777981</v>
       </c>
       <c r="Y36" t="n">
-        <v>916.3053954970014</v>
+        <v>29.92</v>
       </c>
     </row>
     <row r="37">
@@ -7062,76 +7062,76 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1003.596670530486</v>
+        <v>184.4056847276783</v>
       </c>
       <c r="C37" t="n">
-        <v>1055.259969496338</v>
+        <v>307.4376905461141</v>
       </c>
       <c r="D37" t="n">
-        <v>1055.259969496338</v>
+        <v>417.7868346711142</v>
       </c>
       <c r="E37" t="n">
-        <v>1055.259969496338</v>
+        <v>532.6457388825272</v>
       </c>
       <c r="F37" t="n">
-        <v>1055.259969496338</v>
+        <v>654.0367114744627</v>
       </c>
       <c r="G37" t="n">
-        <v>1055.259969496338</v>
+        <v>805.1284626072495</v>
       </c>
       <c r="H37" t="n">
-        <v>1055.259969496338</v>
+        <v>977.5002402256634</v>
       </c>
       <c r="I37" t="n">
-        <v>1055.259969496338</v>
+        <v>984.1339439954812</v>
       </c>
       <c r="J37" t="n">
-        <v>1066.665307034036</v>
+        <v>995.5392815331784</v>
       </c>
       <c r="K37" t="n">
-        <v>1066.665307034036</v>
+        <v>995.5392815331784</v>
       </c>
       <c r="L37" t="n">
-        <v>1066.665307034036</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="M37" t="n">
-        <v>1046.573449184134</v>
+        <v>1046.573449184125</v>
       </c>
       <c r="N37" t="n">
-        <v>972.9258487275557</v>
+        <v>972.9258487275464</v>
       </c>
       <c r="O37" t="n">
-        <v>821.5090014213806</v>
+        <v>821.5090014213713</v>
       </c>
       <c r="P37" t="n">
-        <v>608.9778913530758</v>
+        <v>608.9778913530665</v>
       </c>
       <c r="Q37" t="n">
-        <v>332.7937838524718</v>
+        <v>332.7937838524626</v>
       </c>
       <c r="R37" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="S37" t="n">
-        <v>29.92000000000917</v>
+        <v>75.6183470613862</v>
       </c>
       <c r="T37" t="n">
-        <v>29.92000000000917</v>
+        <v>75.6183470613862</v>
       </c>
       <c r="U37" t="n">
-        <v>273.536930015345</v>
+        <v>75.6183470613862</v>
       </c>
       <c r="V37" t="n">
-        <v>469.388322901291</v>
+        <v>75.6183470613862</v>
       </c>
       <c r="W37" t="n">
-        <v>638.3092411609684</v>
+        <v>75.6183470613862</v>
       </c>
       <c r="X37" t="n">
-        <v>786.370032185162</v>
+        <v>75.6183470613862</v>
       </c>
       <c r="Y37" t="n">
-        <v>894.8093328641943</v>
+        <v>75.6183470613862</v>
       </c>
     </row>
     <row r="38">
@@ -7141,76 +7141,76 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>113.8065837274916</v>
+        <v>117.1408562629478</v>
       </c>
       <c r="C38" t="n">
-        <v>60.80195923961899</v>
+        <v>64.13623177507515</v>
       </c>
       <c r="D38" t="n">
-        <v>47.32806455290203</v>
+        <v>50.66233708835819</v>
       </c>
       <c r="E38" t="n">
-        <v>39.89039828333775</v>
+        <v>43.2246708187939</v>
       </c>
       <c r="F38" t="n">
-        <v>35.25534889151837</v>
+        <v>35.25534889150919</v>
       </c>
       <c r="G38" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="H38" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="I38" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J38" t="n">
-        <v>119.1959849731487</v>
+        <v>119.1959849731395</v>
       </c>
       <c r="K38" t="n">
-        <v>304.9927226113396</v>
+        <v>304.9927226113305</v>
       </c>
       <c r="L38" t="n">
-        <v>535.4900049228974</v>
+        <v>535.4900049228883</v>
       </c>
       <c r="M38" t="n">
-        <v>905.7500049230038</v>
+        <v>739.431587554762</v>
       </c>
       <c r="N38" t="n">
-        <v>1109.691587555266</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O38" t="n">
-        <v>1286.244759641738</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P38" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="Q38" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="R38" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="S38" t="n">
-        <v>1431.123215102929</v>
+        <v>1431.123215102471</v>
       </c>
       <c r="T38" t="n">
-        <v>1246.055417712014</v>
+        <v>1246.055417711555</v>
       </c>
       <c r="U38" t="n">
-        <v>991.4056536737746</v>
+        <v>994.7399262092307</v>
       </c>
       <c r="V38" t="n">
-        <v>756.2025989598111</v>
+        <v>759.5368714952672</v>
       </c>
       <c r="W38" t="n">
-        <v>512.391007059864</v>
+        <v>515.7252795953201</v>
       </c>
       <c r="X38" t="n">
-        <v>315.1366298268663</v>
+        <v>318.4709023623224</v>
       </c>
       <c r="Y38" t="n">
-        <v>199.6644756018093</v>
+        <v>202.9987481372655</v>
       </c>
     </row>
     <row r="39">
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>176.4043156815831</v>
+        <v>1250.913525423656</v>
       </c>
       <c r="C39" t="n">
-        <v>176.4043156815831</v>
+        <v>886.1661391150506</v>
       </c>
       <c r="D39" t="n">
-        <v>29.92000000000917</v>
+        <v>534.7139301274722</v>
       </c>
       <c r="E39" t="n">
-        <v>29.92000000000917</v>
+        <v>534.7139301274722</v>
       </c>
       <c r="F39" t="n">
-        <v>29.92000000000917</v>
+        <v>357.7424055818624</v>
       </c>
       <c r="G39" t="n">
-        <v>29.92000000000917</v>
+        <v>357.7424055818624</v>
       </c>
       <c r="H39" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="I39" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J39" t="n">
-        <v>174.7530143488394</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K39" t="n">
-        <v>197.2198694416696</v>
+        <v>543.0996394772296</v>
       </c>
       <c r="L39" t="n">
-        <v>567.4798694417759</v>
+        <v>599.927050901758</v>
       </c>
       <c r="M39" t="n">
-        <v>851.5752611846351</v>
+        <v>744.4012057393636</v>
       </c>
       <c r="N39" t="n">
-        <v>1188.111259660128</v>
+        <v>1080.937204214856</v>
       </c>
       <c r="O39" t="n">
-        <v>1234.237999493216</v>
+        <v>1451.197204214901</v>
       </c>
       <c r="P39" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="Q39" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="R39" t="n">
-        <v>1393.715165685686</v>
+        <v>1393.715165685228</v>
       </c>
       <c r="S39" t="n">
-        <v>1338.259295700468</v>
+        <v>1338.259295700009</v>
       </c>
       <c r="T39" t="n">
-        <v>1333.03106897037</v>
+        <v>1333.031068969912</v>
       </c>
       <c r="U39" t="n">
-        <v>1329.84073988156</v>
+        <v>1329.840739881101</v>
       </c>
       <c r="V39" t="n">
-        <v>1312.153197263862</v>
+        <v>1312.153197263404</v>
       </c>
       <c r="W39" t="n">
-        <v>934.3754194859762</v>
+        <v>1276.422749879739</v>
       </c>
       <c r="X39" t="n">
-        <v>556.5976417080899</v>
+        <v>1253.329073672277</v>
       </c>
       <c r="Y39" t="n">
-        <v>554.1820934594693</v>
+        <v>1250.913525423656</v>
       </c>
     </row>
     <row r="40">
@@ -7299,76 +7299,76 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="C40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="D40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="E40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="F40" t="n">
-        <v>151.3109725919446</v>
+        <v>189.426731231158</v>
       </c>
       <c r="G40" t="n">
-        <v>302.4027237247316</v>
+        <v>340.5184823639449</v>
       </c>
       <c r="H40" t="n">
-        <v>302.4027237247316</v>
+        <v>512.8902599823589</v>
       </c>
       <c r="I40" t="n">
-        <v>540.2688098739293</v>
+        <v>512.8902599823589</v>
       </c>
       <c r="J40" t="n">
-        <v>883.1502599824131</v>
+        <v>883.150259982404</v>
       </c>
       <c r="K40" t="n">
-        <v>1066.665307034036</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="L40" t="n">
-        <v>1066.665307034036</v>
+        <v>1066.665307034026</v>
       </c>
       <c r="M40" t="n">
-        <v>1046.573449184134</v>
+        <v>1046.573449184125</v>
       </c>
       <c r="N40" t="n">
-        <v>972.9258487275557</v>
+        <v>972.9258487275466</v>
       </c>
       <c r="O40" t="n">
-        <v>821.5090014213806</v>
+        <v>821.5090014213715</v>
       </c>
       <c r="P40" t="n">
-        <v>608.9778913530758</v>
+        <v>608.9778913530666</v>
       </c>
       <c r="Q40" t="n">
-        <v>332.7937838524718</v>
+        <v>332.7937838524626</v>
       </c>
       <c r="R40" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="S40" t="n">
-        <v>29.92000000000917</v>
+        <v>75.61834706138623</v>
       </c>
       <c r="T40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="U40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="V40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="W40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="X40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
       <c r="Y40" t="n">
-        <v>29.92000000000917</v>
+        <v>189.426731231158</v>
       </c>
     </row>
     <row r="41">
@@ -7378,76 +7378,76 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29.92000000000917</v>
+        <v>422.5637924273681</v>
       </c>
       <c r="C41" t="n">
-        <v>29.92000000000917</v>
+        <v>371.3184249993056</v>
       </c>
       <c r="D41" t="n">
-        <v>29.92000000000917</v>
+        <v>252.7940252620836</v>
       </c>
       <c r="E41" t="n">
-        <v>29.92000000000917</v>
+        <v>140.3058539420143</v>
       </c>
       <c r="F41" t="n">
-        <v>29.92000000000917</v>
+        <v>140.3058539420143</v>
       </c>
       <c r="G41" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="H41" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="I41" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J41" t="n">
-        <v>119.1959849731487</v>
+        <v>400.1800000000685</v>
       </c>
       <c r="K41" t="n">
-        <v>304.9927226113396</v>
+        <v>585.9767376382595</v>
       </c>
       <c r="L41" t="n">
-        <v>535.4900049228974</v>
+        <v>956.2367376382595</v>
       </c>
       <c r="M41" t="n">
-        <v>739.4315875550999</v>
+        <v>956.2367376382595</v>
       </c>
       <c r="N41" t="n">
-        <v>1109.691587555266</v>
+        <v>1109.691587554807</v>
       </c>
       <c r="O41" t="n">
-        <v>1286.244759641738</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P41" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="Q41" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="R41" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="S41" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="T41" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="U41" t="n">
-        <v>1136.299730911714</v>
+        <v>1136.299730911256</v>
       </c>
       <c r="V41" t="n">
-        <v>796.0461711472457</v>
+        <v>1136.299730911256</v>
       </c>
       <c r="W41" t="n">
-        <v>447.1840741967936</v>
+        <v>1136.299730911256</v>
       </c>
       <c r="X41" t="n">
-        <v>250.4426592755712</v>
+        <v>833.9948486277528</v>
       </c>
       <c r="Y41" t="n">
-        <v>29.92000000000917</v>
+        <v>613.4721893521909</v>
       </c>
     </row>
     <row r="42">
@@ -7457,76 +7457,76 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>315.6172324016935</v>
+        <v>315.6172324016843</v>
       </c>
       <c r="C42" t="n">
-        <v>246.829442052684</v>
+        <v>246.8294420526749</v>
       </c>
       <c r="D42" t="n">
-        <v>191.3368290247016</v>
+        <v>191.3368290246924</v>
       </c>
       <c r="E42" t="n">
-        <v>141.1629934470121</v>
+        <v>141.1629934470029</v>
       </c>
       <c r="F42" t="n">
-        <v>94.05567795420717</v>
+        <v>94.05567795419802</v>
       </c>
       <c r="G42" t="n">
-        <v>61.78280962227561</v>
+        <v>61.78280962226644</v>
       </c>
       <c r="H42" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="I42" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J42" t="n">
-        <v>227.7113459300251</v>
+        <v>29.92</v>
       </c>
       <c r="K42" t="n">
-        <v>543.0996394772387</v>
+        <v>52.38685509283023</v>
       </c>
       <c r="L42" t="n">
-        <v>599.9270509017671</v>
+        <v>422.6468550928987</v>
       </c>
       <c r="M42" t="n">
-        <v>884.0224426446264</v>
+        <v>706.7422468357579</v>
       </c>
       <c r="N42" t="n">
-        <v>1188.111259660128</v>
+        <v>863.9779994926889</v>
       </c>
       <c r="O42" t="n">
-        <v>1234.237999493216</v>
+        <v>1234.237999492757</v>
       </c>
       <c r="P42" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="Q42" t="n">
-        <v>1493.589117731903</v>
+        <v>1496</v>
       </c>
       <c r="R42" t="n">
-        <v>1286.253778366626</v>
+        <v>1288.664660634723</v>
       </c>
       <c r="S42" t="n">
-        <v>1125.747403330902</v>
+        <v>1128.158285598999</v>
       </c>
       <c r="T42" t="n">
-        <v>1015.468671550299</v>
+        <v>1015.46867155029</v>
       </c>
       <c r="U42" t="n">
-        <v>907.2278374109836</v>
+        <v>907.2278374109744</v>
       </c>
       <c r="V42" t="n">
-        <v>784.4897897427815</v>
+        <v>784.4897897427722</v>
       </c>
       <c r="W42" t="n">
-        <v>643.7088373086112</v>
+        <v>643.708837308602</v>
       </c>
       <c r="X42" t="n">
-        <v>515.564656050644</v>
+        <v>515.5646560506348</v>
       </c>
       <c r="Y42" t="n">
-        <v>408.0986027515183</v>
+        <v>408.0986027515092</v>
       </c>
     </row>
     <row r="43">
@@ -7536,76 +7536,76 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>470.7817775581435</v>
+        <v>470.7817775581344</v>
       </c>
       <c r="C43" t="n">
-        <v>490.8537833765793</v>
+        <v>490.8537833765702</v>
       </c>
       <c r="D43" t="n">
-        <v>498.2429275015794</v>
+        <v>498.2429275015703</v>
       </c>
       <c r="E43" t="n">
-        <v>510.1418317129924</v>
+        <v>510.1418317129833</v>
       </c>
       <c r="F43" t="n">
-        <v>528.5728043049279</v>
+        <v>528.5728043049188</v>
       </c>
       <c r="G43" t="n">
-        <v>576.7045554377148</v>
+        <v>576.7045554377057</v>
       </c>
       <c r="H43" t="n">
-        <v>646.1163330561287</v>
+        <v>646.1163330561196</v>
       </c>
       <c r="I43" t="n">
-        <v>781.0224192053264</v>
+        <v>781.0224192053173</v>
       </c>
       <c r="J43" t="n">
-        <v>1082.497756743024</v>
+        <v>1082.497756743015</v>
       </c>
       <c r="K43" t="n">
-        <v>1163.052803794646</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="L43" t="n">
-        <v>1130.572470666239</v>
+        <v>1161.48146711223</v>
       </c>
       <c r="M43" t="n">
-        <v>1005.430107765832</v>
+        <v>1161.48146711223</v>
       </c>
       <c r="N43" t="n">
-        <v>826.7320022587488</v>
+        <v>1161.48146711223</v>
       </c>
       <c r="O43" t="n">
-        <v>570.2646499020686</v>
+        <v>1161.48146711223</v>
       </c>
       <c r="P43" t="n">
-        <v>252.6830347832587</v>
+        <v>843.8998519934198</v>
       </c>
       <c r="Q43" t="n">
-        <v>29.92000000000917</v>
+        <v>466.1220742155722</v>
       </c>
       <c r="R43" t="n">
-        <v>29.92000000000917</v>
+        <v>88.34429643772449</v>
       </c>
       <c r="S43" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="T43" t="n">
-        <v>114.8651070276665</v>
+        <v>114.8651070276573</v>
       </c>
       <c r="U43" t="n">
-        <v>255.5220370430023</v>
+        <v>255.5220370429931</v>
       </c>
       <c r="V43" t="n">
-        <v>348.4134299289482</v>
+        <v>348.4134299289391</v>
       </c>
       <c r="W43" t="n">
-        <v>414.3743481886256</v>
+        <v>414.3743481886165</v>
       </c>
       <c r="X43" t="n">
-        <v>459.4751392128192</v>
+        <v>459.4751392128101</v>
       </c>
       <c r="Y43" t="n">
-        <v>464.9544398918514</v>
+        <v>464.9544398918423</v>
       </c>
     </row>
     <row r="44">
@@ -7615,76 +7615,76 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>255.4279982978683</v>
+        <v>434.7503722694506</v>
       </c>
       <c r="C44" t="n">
-        <v>255.4279982978683</v>
+        <v>434.7503722694506</v>
       </c>
       <c r="D44" t="n">
-        <v>255.4279982978683</v>
+        <v>316.2259725322285</v>
       </c>
       <c r="E44" t="n">
-        <v>142.9398269777989</v>
+        <v>316.2259725322285</v>
       </c>
       <c r="F44" t="n">
-        <v>29.92000000000917</v>
+        <v>241.2148995843773</v>
       </c>
       <c r="G44" t="n">
-        <v>29.92000000000917</v>
+        <v>130.8290456423631</v>
       </c>
       <c r="H44" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="I44" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J44" t="n">
-        <v>119.1959849731487</v>
+        <v>400.1800000001513</v>
       </c>
       <c r="K44" t="n">
-        <v>304.9927226113396</v>
+        <v>770.4400000001513</v>
       </c>
       <c r="L44" t="n">
-        <v>535.4900049228974</v>
+        <v>1000.937282311709</v>
       </c>
       <c r="M44" t="n">
-        <v>905.7500049230109</v>
+        <v>1000.937282311709</v>
       </c>
       <c r="N44" t="n">
-        <v>1109.691587555266</v>
+        <v>1000.937282311709</v>
       </c>
       <c r="O44" t="n">
-        <v>1286.244759641738</v>
+        <v>1286.24475964128</v>
       </c>
       <c r="P44" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="Q44" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="R44" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="S44" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="T44" t="n">
-        <v>1496.000000000459</v>
+        <v>1205.88169755858</v>
       </c>
       <c r="U44" t="n">
-        <v>1136.299730911714</v>
+        <v>846.1814284698353</v>
       </c>
       <c r="V44" t="n">
-        <v>906.5949775318231</v>
+        <v>846.1814284698353</v>
       </c>
       <c r="W44" t="n">
-        <v>557.7328805813711</v>
+        <v>846.1814284698353</v>
       </c>
       <c r="X44" t="n">
-        <v>255.4279982978683</v>
+        <v>846.1814284698353</v>
       </c>
       <c r="Y44" t="n">
-        <v>255.4279982978683</v>
+        <v>625.6587691942733</v>
       </c>
     </row>
     <row r="45">
@@ -7694,76 +7694,76 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>315.6172324016935</v>
+        <v>315.6172324016843</v>
       </c>
       <c r="C45" t="n">
-        <v>246.829442052684</v>
+        <v>246.8294420526749</v>
       </c>
       <c r="D45" t="n">
-        <v>191.3368290247016</v>
+        <v>191.3368290246924</v>
       </c>
       <c r="E45" t="n">
-        <v>141.1629934470121</v>
+        <v>141.1629934470029</v>
       </c>
       <c r="F45" t="n">
-        <v>94.05567795420717</v>
+        <v>94.05567795419802</v>
       </c>
       <c r="G45" t="n">
-        <v>61.78280962227559</v>
+        <v>61.78280962226643</v>
       </c>
       <c r="H45" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="I45" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="J45" t="n">
-        <v>227.7113459300251</v>
+        <v>227.711345930016</v>
       </c>
       <c r="K45" t="n">
-        <v>543.0996394772387</v>
+        <v>250.1782010228462</v>
       </c>
       <c r="L45" t="n">
-        <v>744.4012057397538</v>
+        <v>620.4382010229975</v>
       </c>
       <c r="M45" t="n">
-        <v>744.4012057397538</v>
+        <v>620.4382010229975</v>
       </c>
       <c r="N45" t="n">
-        <v>1080.937204215247</v>
+        <v>956.9741994984903</v>
       </c>
       <c r="O45" t="n">
-        <v>1451.19720421536</v>
+        <v>1234.237999492757</v>
       </c>
       <c r="P45" t="n">
-        <v>1496.000000000459</v>
+        <v>1496</v>
       </c>
       <c r="Q45" t="n">
-        <v>1493.589117731903</v>
+        <v>1493.589117731894</v>
       </c>
       <c r="R45" t="n">
-        <v>1286.253778366626</v>
+        <v>1286.253778366616</v>
       </c>
       <c r="S45" t="n">
-        <v>1125.747403330902</v>
+        <v>1125.747403330893</v>
       </c>
       <c r="T45" t="n">
-        <v>1015.468671550299</v>
+        <v>1015.46867155029</v>
       </c>
       <c r="U45" t="n">
-        <v>907.2278374109836</v>
+        <v>907.2278374109744</v>
       </c>
       <c r="V45" t="n">
-        <v>784.4897897427815</v>
+        <v>784.4897897427722</v>
       </c>
       <c r="W45" t="n">
-        <v>643.7088373086112</v>
+        <v>643.708837308602</v>
       </c>
       <c r="X45" t="n">
-        <v>515.564656050644</v>
+        <v>515.5646560506348</v>
       </c>
       <c r="Y45" t="n">
-        <v>408.0986027515183</v>
+        <v>408.0986027515092</v>
       </c>
     </row>
     <row r="46">
@@ -7773,76 +7773,76 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>470.7817775581435</v>
+        <v>470.7817775581344</v>
       </c>
       <c r="C46" t="n">
-        <v>490.8537833765793</v>
+        <v>490.8537833765702</v>
       </c>
       <c r="D46" t="n">
-        <v>498.2429275015794</v>
+        <v>498.2429275015703</v>
       </c>
       <c r="E46" t="n">
-        <v>510.1418317129924</v>
+        <v>510.1418317129833</v>
       </c>
       <c r="F46" t="n">
-        <v>528.5728043049279</v>
+        <v>528.5728043049188</v>
       </c>
       <c r="G46" t="n">
-        <v>576.7045554377148</v>
+        <v>576.7045554377057</v>
       </c>
       <c r="H46" t="n">
-        <v>646.1163330561287</v>
+        <v>646.1163330561196</v>
       </c>
       <c r="I46" t="n">
-        <v>781.0224192053264</v>
+        <v>781.0224192053173</v>
       </c>
       <c r="J46" t="n">
-        <v>1082.497756743024</v>
+        <v>1082.497756743015</v>
       </c>
       <c r="K46" t="n">
-        <v>1163.052803794646</v>
+        <v>1163.052803794637</v>
       </c>
       <c r="L46" t="n">
-        <v>1130.572470666239</v>
+        <v>1130.57247066623</v>
       </c>
       <c r="M46" t="n">
-        <v>1130.572470666239</v>
+        <v>1005.430107765823</v>
       </c>
       <c r="N46" t="n">
-        <v>1040.171041691117</v>
+        <v>826.7320022587398</v>
       </c>
       <c r="O46" t="n">
-        <v>783.7036893344373</v>
+        <v>570.2646499020598</v>
       </c>
       <c r="P46" t="n">
-        <v>466.1220742156273</v>
+        <v>570.2646499020598</v>
       </c>
       <c r="Q46" t="n">
-        <v>466.1220742156273</v>
+        <v>466.1220742156568</v>
       </c>
       <c r="R46" t="n">
-        <v>88.34429643773369</v>
+        <v>88.34429643772452</v>
       </c>
       <c r="S46" t="n">
-        <v>29.92000000000917</v>
+        <v>29.92</v>
       </c>
       <c r="T46" t="n">
-        <v>114.8651070276665</v>
+        <v>114.8651070276573</v>
       </c>
       <c r="U46" t="n">
-        <v>255.5220370430023</v>
+        <v>255.5220370429931</v>
       </c>
       <c r="V46" t="n">
-        <v>348.4134299289482</v>
+        <v>348.4134299289391</v>
       </c>
       <c r="W46" t="n">
-        <v>414.3743481886256</v>
+        <v>414.3743481886165</v>
       </c>
       <c r="X46" t="n">
-        <v>459.4751392128192</v>
+        <v>459.4751392128101</v>
       </c>
       <c r="Y46" t="n">
-        <v>464.9544398918514</v>
+        <v>464.9544398918423</v>
       </c>
     </row>
   </sheetData>
@@ -7964,10 +7964,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>242.2604579480496</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>321.8400703517588</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -7976,16 +7976,16 @@
         <v>472.2608914614128</v>
       </c>
       <c r="N2" t="n">
-        <v>778.0826666125488</v>
+        <v>639.5838718235262</v>
       </c>
       <c r="O2" t="n">
-        <v>375.1590153027356</v>
+        <v>1.159015302735668</v>
       </c>
       <c r="P2" t="n">
-        <v>315.3213213472141</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>128.5418702571336</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R2" t="n">
         <v>294.54111633436</v>
@@ -8204,25 +8204,25 @@
         <v>0.2405037325275146</v>
       </c>
       <c r="K5" t="n">
-        <v>183.3412755627362</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>846.2608914614127</v>
+        <v>714.2808456769349</v>
       </c>
       <c r="N5" t="n">
         <v>778.0826666125488</v>
       </c>
       <c r="O5" t="n">
-        <v>1.159015302735668</v>
+        <v>375.1590153027356</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>315.3213213472141</v>
       </c>
       <c r="Q5" t="n">
-        <v>502.5418702571336</v>
+        <v>128.5418702571336</v>
       </c>
       <c r="R5" t="n">
         <v>294.54111633436</v>
@@ -8438,16 +8438,16 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2405037325275146</v>
+        <v>374.2405037325275</v>
       </c>
       <c r="K8" t="n">
-        <v>321.8400703517588</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>846.2608914614127</v>
+        <v>655.6021670241489</v>
       </c>
       <c r="N8" t="n">
         <v>778.0826666125488</v>
@@ -8459,7 +8459,7 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>364.0430754681111</v>
+        <v>502.5418702571336</v>
       </c>
       <c r="R8" t="n">
         <v>294.54111633436</v>
@@ -8675,28 +8675,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>170.5050864162441</v>
       </c>
       <c r="L11" t="n">
-        <v>422.1744623115578</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>470.3677206523834</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N11" t="n">
-        <v>868.993772140187</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>476.6634625389171</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>443.126019839677</v>
       </c>
       <c r="Q11" t="n">
-        <v>13.49857879984722</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,19 +8912,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>467.3265276381908</v>
+        <v>467.326527638191</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>285.1988562855334</v>
+        <v>940.198856285534</v>
       </c>
       <c r="N14" t="n">
-        <v>406.6570767106775</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8933,7 +8933,7 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>615.8520732695737</v>
+        <v>583.82011442622</v>
       </c>
       <c r="R14" t="n">
         <v>294.54111633436</v>
@@ -9158,10 +9158,10 @@
         <v>422.1744623115577</v>
       </c>
       <c r="M17" t="n">
-        <v>940.1988562855336</v>
+        <v>940.198856285534</v>
       </c>
       <c r="N17" t="n">
-        <v>227.1138786234671</v>
+        <v>829.4673730931931</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -9170,7 +9170,7 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>615.8520732695737</v>
+        <v>13.49857879984722</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,19 +9389,19 @@
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>422.1744623115576</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>940.1988562855372</v>
+        <v>940.198856285534</v>
       </c>
       <c r="N20" t="n">
-        <v>362.1408454550733</v>
+        <v>868.9937721401875</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>382.6480632645631</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -9623,25 +9623,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>467.326527638191</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>422.1744623115576</v>
+        <v>422.1744623115578</v>
       </c>
       <c r="M23" t="n">
-        <v>285.1988562855334</v>
+        <v>682.2417008127065</v>
       </c>
       <c r="N23" t="n">
-        <v>574.0148256153172</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>443.1260198396857</v>
+        <v>443.126019839677</v>
       </c>
       <c r="Q23" t="n">
         <v>13.49857879984722</v>
@@ -9869,16 +9869,16 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>940.1988562855499</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N26" t="n">
-        <v>218.9836043493055</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>476.6634625389166</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>183.3263696697644</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10100,13 +10100,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>467.3265276383056</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>422.1744623115578</v>
       </c>
       <c r="M29" t="n">
-        <v>940.1988562855611</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N29" t="n">
         <v>213.993772140187</v>
@@ -10115,10 +10115,10 @@
         <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>140.0167990405285</v>
+        <v>443.1260198396793</v>
       </c>
       <c r="Q29" t="n">
-        <v>13.49857879984722</v>
+        <v>410.541423327018</v>
       </c>
       <c r="R29" t="n">
         <v>294.54111633436</v>
@@ -10337,25 +10337,25 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>467.3265276383055</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>940.1988562855736</v>
+        <v>940.1988562855372</v>
       </c>
       <c r="N32" t="n">
-        <v>341.1892879271431</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>476.6634625389203</v>
       </c>
       <c r="P32" t="n">
-        <v>443.1260198397166</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>13.49857879984722</v>
+        <v>574.4831795254876</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10577,16 +10577,16 @@
         <v>0</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>10.33813607914311</v>
       </c>
       <c r="M35" t="n">
-        <v>659.1988562856063</v>
+        <v>659.1988562855536</v>
       </c>
       <c r="N35" t="n">
-        <v>419.9953707585136</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>195.6634625389367</v>
       </c>
       <c r="P35" t="n">
         <v>0</v>
@@ -10656,19 +10656,19 @@
         <v>295.8802408630135</v>
       </c>
       <c r="L36" t="n">
-        <v>316.5985743187311</v>
+        <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>341.4720271841035</v>
+        <v>471.6948204301074</v>
       </c>
       <c r="N36" t="n">
-        <v>485.4085271713503</v>
+        <v>145.473175175903</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>307.1604212273249</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q36" t="n">
         <v>17.27519534353338</v>
@@ -10817,10 +10817,10 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>659.1988562856409</v>
+        <v>491.2004549035876</v>
       </c>
       <c r="N38" t="n">
-        <v>419.9953707586334</v>
+        <v>587.9937721402325</v>
       </c>
       <c r="O38" t="n">
         <v>0</v>
@@ -10887,25 +10887,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J39" t="n">
-        <v>173.9714777043685</v>
+        <v>227.4647419277884</v>
       </c>
       <c r="K39" t="n">
-        <v>0</v>
+        <v>295.8802408630135</v>
       </c>
       <c r="L39" t="n">
-        <v>316.5985743187657</v>
+        <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>471.6948204301074</v>
+        <v>330.6632680005583</v>
       </c>
       <c r="N39" t="n">
         <v>485.4085271713503</v>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>327.4073335019765</v>
       </c>
       <c r="P39" t="n">
-        <v>219.1507118405495</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
         <v>17.27519534353338</v>
@@ -11045,19 +11045,19 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>283.8222374009384</v>
       </c>
       <c r="K41" t="n">
         <v>0</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>141.1744623115578</v>
       </c>
       <c r="M41" t="n">
-        <v>491.2004549039197</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N41" t="n">
-        <v>587.9937721403544</v>
+        <v>368.9986710457906</v>
       </c>
       <c r="O41" t="n">
         <v>0</v>
@@ -11124,22 +11124,22 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J42" t="n">
-        <v>227.4647419277884</v>
+        <v>27.675503614641</v>
       </c>
       <c r="K42" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
-        <v>0</v>
+        <v>316.5985743187275</v>
       </c>
       <c r="M42" t="n">
         <v>471.6948204301074</v>
       </c>
       <c r="N42" t="n">
-        <v>452.6335964036823</v>
+        <v>304.2971677586616</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>327.4073335020001</v>
       </c>
       <c r="P42" t="n">
         <v>219.1507118405495</v>
@@ -11282,22 +11282,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>283.8222374010221</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>186.326527638191</v>
       </c>
       <c r="L44" t="n">
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>659.1988562856482</v>
+        <v>285.1988562855334</v>
       </c>
       <c r="N44" t="n">
-        <v>419.9953707586261</v>
+        <v>213.993772140187</v>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>109.8528335788868</v>
       </c>
       <c r="P44" t="n">
         <v>0</v>
@@ -11364,10 +11364,10 @@
         <v>227.4647419277884</v>
       </c>
       <c r="K45" t="n">
-        <v>295.8802408630135</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>145.9334897353402</v>
+        <v>316.5985743188111</v>
       </c>
       <c r="M45" t="n">
         <v>184.7297782656032</v>
@@ -11376,10 +11376,10 @@
         <v>485.4085271713503</v>
       </c>
       <c r="O45" t="n">
-        <v>327.4073335020456</v>
+        <v>233.4717779405845</v>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>219.1507118405495</v>
       </c>
       <c r="Q45" t="n">
         <v>17.27519534353338</v>
@@ -23232,7 +23232,7 @@
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.6960849964949034</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -23241,7 +23241,7 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>0.6960849964948608</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23429,10 +23429,10 @@
         <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.850361477466265</v>
       </c>
       <c r="S13" t="n">
-        <v>2.85036147746635</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23475,10 +23475,10 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.6960849964948983</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23669,7 +23669,7 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.850361477465452</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23712,10 +23712,10 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.696084996494875</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>0.6960849964948608</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -23906,7 +23906,7 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.850361477464968</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23952,7 +23952,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -24143,7 +24143,7 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.850361477466322</v>
+        <v>2.85036147746635</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.696084996495216</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24237,7 +24237,7 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="Y23" t="n">
         <v>0</v>
@@ -24359,7 +24359,7 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
-        <v>2.850361477466352</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24423,7 +24423,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -24459,7 +24459,7 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6960849960503879</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>0</v>
@@ -24596,7 +24596,7 @@
         <v>0</v>
       </c>
       <c r="L28" t="n">
-        <v>2.850361477466112</v>
+        <v>2.850361477466352</v>
       </c>
       <c r="M28" t="n">
         <v>0</v>
@@ -24660,10 +24660,10 @@
         <v>0</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.696084996494875</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6960849960501889</v>
+        <v>0</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24839,7 +24839,7 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>2.850361477466123</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -24894,10 +24894,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.6960849964949034</v>
       </c>
       <c r="G32" t="n">
-        <v>0.6960849960501838</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -25082,13 +25082,13 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>2.850361477465924</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.850361477466322</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -25131,7 +25131,7 @@
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>3.300929810261938</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -25170,7 +25170,7 @@
         <v>0</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>3.300929810555601</v>
       </c>
       <c r="T35" t="n">
         <v>0</v>
@@ -25368,7 +25368,7 @@
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>3.30092981011067</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -25413,7 +25413,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>3.300929810555573</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -25593,22 +25593,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
-        <v>156.4745782429939</v>
+        <v>105.7416644892121</v>
       </c>
       <c r="D41" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
-        <v>111.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
         <v>111.8896287080119</v>
       </c>
       <c r="G41" t="n">
-        <v>109.2819954025941</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
         <v>99.89995518593948</v>
@@ -25653,13 +25653,13 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X41" t="n">
-        <v>104.5078326886575</v>
+        <v>0</v>
       </c>
       <c r="Y41" t="n">
         <v>0</v>
@@ -25781,28 +25781,28 @@
         <v>0</v>
       </c>
       <c r="L43" t="n">
-        <v>0</v>
+        <v>30.59990648154002</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>123.8909392714024</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>176.9111244520127</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>253.9026788331133</v>
       </c>
       <c r="P43" t="n">
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>156.8868619901809</v>
+        <v>3.422266425528761</v>
       </c>
       <c r="R43" t="n">
-        <v>403.845046013938</v>
+        <v>29.84504601386872</v>
       </c>
       <c r="S43" t="n">
-        <v>57.84005347334724</v>
+        <v>0</v>
       </c>
       <c r="T43" t="n">
         <v>0</v>
@@ -25830,25 +25830,25 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>188.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
         <v>156.4745782429939</v>
       </c>
       <c r="D44" t="n">
-        <v>117.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>111.3632896068686</v>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>37.62866648963916</v>
       </c>
       <c r="G44" t="n">
-        <v>109.2819954025941</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>99.89995518593946</v>
+        <v>0</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -25884,22 +25884,22 @@
         <v>168.2280170485541</v>
       </c>
       <c r="T44" t="n">
-        <v>287.2171194170061</v>
+        <v>0</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>109.4433183207317</v>
+        <v>336.8510241668239</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>345.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>299.2818334606677</v>
       </c>
       <c r="Y44" t="n">
-        <v>218.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -26021,22 +26021,22 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>123.8909392714024</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
-        <v>87.41370976664246</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
         <v>0</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>314.4057989676218</v>
       </c>
       <c r="Q46" t="n">
-        <v>377.422266425598</v>
+        <v>274.321116496059</v>
       </c>
       <c r="R46" t="n">
-        <v>29.84504601382332</v>
+        <v>29.84504601378507</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7808824.686420076</v>
+        <v>7808824.686420074</v>
       </c>
     </row>
     <row r="9">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10012517.82718008</v>
+        <v>10012517.82718004</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>11114364.3975601</v>
+        <v>11114364.39756002</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>12216210.96794012</v>
+        <v>12216210.96794002</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13281144.86493422</v>
+        <v>13281144.8649341</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14382869.86546398</v>
+        <v>14382869.86546382</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>15370480.02292401</v>
+        <v>15370480.02292381</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>16358090.18038404</v>
+        <v>16358090.18038381</v>
       </c>
     </row>
   </sheetData>
@@ -26269,13 +26269,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1101954.910291021</v>
+        <v>1101954.91029102</v>
       </c>
       <c r="C2" t="n">
         <v>1101954.910291021</v>
       </c>
       <c r="D2" t="n">
-        <v>1101954.91029102</v>
+        <v>1101954.910291021</v>
       </c>
       <c r="E2" t="n">
         <v>1101846.570379988</v>
@@ -26293,25 +26293,25 @@
         <v>1101846.570379988</v>
       </c>
       <c r="J2" t="n">
-        <v>1101846.570380019</v>
+        <v>1101846.570379989</v>
       </c>
       <c r="K2" t="n">
-        <v>1101846.570380019</v>
+        <v>1101846.570379988</v>
       </c>
       <c r="L2" t="n">
-        <v>1101846.570380018</v>
+        <v>1101846.570379988</v>
       </c>
       <c r="M2" t="n">
-        <v>1101725.000529736</v>
+        <v>1101725.000529716</v>
       </c>
       <c r="N2" t="n">
-        <v>1101725.000529747</v>
+        <v>1101725.000529716</v>
       </c>
       <c r="O2" t="n">
-        <v>987610.1574600189</v>
+        <v>987610.1574599884</v>
       </c>
       <c r="P2" t="n">
-        <v>987610.1574600185</v>
+        <v>987610.1574599878</v>
       </c>
     </row>
     <row r="3">
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>386848.0000000403</v>
+        <v>386848</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>602419.1762101186</v>
+        <v>602219.8615549038</v>
       </c>
       <c r="C4" t="n">
-        <v>600410.2540226299</v>
+        <v>600210.9393674152</v>
       </c>
       <c r="D4" t="n">
-        <v>598398.606606806</v>
+        <v>598199.2919515911</v>
       </c>
       <c r="E4" t="n">
-        <v>508463.6174685807</v>
+        <v>508269.4590428486</v>
       </c>
       <c r="F4" t="n">
-        <v>506794.9519687438</v>
+        <v>506600.7935430115</v>
       </c>
       <c r="G4" t="n">
-        <v>505123.9837731232</v>
+        <v>504929.8253473911</v>
       </c>
       <c r="H4" t="n">
-        <v>503450.6963689979</v>
+        <v>503256.5379432672</v>
       </c>
       <c r="I4" t="n">
-        <v>501775.0730285004</v>
+        <v>501580.9146027682</v>
       </c>
       <c r="J4" t="n">
-        <v>500097.0968045329</v>
+        <v>499902.9383787895</v>
       </c>
       <c r="K4" t="n">
-        <v>498416.7505265612</v>
+        <v>498222.5921008178</v>
       </c>
       <c r="L4" t="n">
-        <v>496734.0167963866</v>
+        <v>496539.8583706431</v>
       </c>
       <c r="M4" t="n">
-        <v>522490.4615842192</v>
+        <v>522371.0444804642</v>
       </c>
       <c r="N4" t="n">
-        <v>520523.3308731564</v>
+        <v>520403.913769399</v>
       </c>
       <c r="O4" t="n">
-        <v>447790.3844156002</v>
+        <v>447670.9673118427</v>
       </c>
       <c r="P4" t="n">
-        <v>446122.6297523548</v>
+        <v>446003.2126485973</v>
       </c>
     </row>
     <row r="5">
@@ -26449,25 +26449,25 @@
         <v>74642.611</v>
       </c>
       <c r="J5" t="n">
-        <v>74642.61100000696</v>
+        <v>74642.611</v>
       </c>
       <c r="K5" t="n">
-        <v>74642.61100000696</v>
+        <v>74642.611</v>
       </c>
       <c r="L5" t="n">
-        <v>74642.61100000696</v>
+        <v>74642.611</v>
       </c>
       <c r="M5" t="n">
-        <v>64115.19300000697</v>
+        <v>64115.193</v>
       </c>
       <c r="N5" t="n">
-        <v>64115.19300000697</v>
+        <v>64115.193</v>
       </c>
       <c r="O5" t="n">
-        <v>55372.01700000698</v>
+        <v>55372.01700000001</v>
       </c>
       <c r="P5" t="n">
-        <v>55372.01700000698</v>
+        <v>55372.01700000001</v>
       </c>
     </row>
     <row r="6">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>209847.334080902</v>
+        <v>210046.6487361165</v>
       </c>
       <c r="C6" t="n">
-        <v>442954.2562683906</v>
+        <v>443153.5709236058</v>
       </c>
       <c r="D6" t="n">
-        <v>444965.903684214</v>
+        <v>445165.2183394294</v>
       </c>
       <c r="E6" t="n">
-        <v>-93746.65808859243</v>
+        <v>-93552.49966286097</v>
       </c>
       <c r="F6" t="n">
-        <v>520409.0074112443</v>
+        <v>520603.1658369766</v>
       </c>
       <c r="G6" t="n">
-        <v>522079.9756068646</v>
+        <v>522274.134032597</v>
       </c>
       <c r="H6" t="n">
-        <v>523753.2630109899</v>
+        <v>523947.4214367208</v>
       </c>
       <c r="I6" t="n">
-        <v>525428.8863514874</v>
+        <v>525623.0447772199</v>
       </c>
       <c r="J6" t="n">
-        <v>140258.8625754391</v>
+        <v>140453.021001199</v>
       </c>
       <c r="K6" t="n">
-        <v>528787.2088534511</v>
+        <v>528981.3672791701</v>
       </c>
       <c r="L6" t="n">
-        <v>530469.9425836247</v>
+        <v>530664.1010093447</v>
       </c>
       <c r="M6" t="n">
-        <v>452719.3459455096</v>
+        <v>452838.7630492516</v>
       </c>
       <c r="N6" t="n">
-        <v>517086.4766565836</v>
+        <v>517205.8937603165</v>
       </c>
       <c r="O6" t="n">
-        <v>312447.7560444117</v>
+        <v>312567.1731481457</v>
       </c>
       <c r="P6" t="n">
-        <v>486115.5107076569</v>
+        <v>486234.9278113905</v>
       </c>
     </row>
   </sheetData>
@@ -26883,25 +26883,25 @@
         <v>655</v>
       </c>
       <c r="J4" t="n">
-        <v>655.0000000001146</v>
+        <v>655</v>
       </c>
       <c r="K4" t="n">
-        <v>655.0000000001146</v>
+        <v>655</v>
       </c>
       <c r="L4" t="n">
-        <v>655.0000000001146</v>
+        <v>655</v>
       </c>
       <c r="M4" t="n">
-        <v>374.0000000001147</v>
+        <v>374</v>
       </c>
       <c r="N4" t="n">
-        <v>374.0000000001147</v>
+        <v>374</v>
       </c>
       <c r="O4" t="n">
-        <v>374.0000000001147</v>
+        <v>374</v>
       </c>
       <c r="P4" t="n">
-        <v>374.0000000001147</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -26984,10 +26984,10 @@
         <v>319</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
         <v>-0</v>
@@ -26999,16 +26999,16 @@
         <v>319</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M2" t="n">
         <v>78</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O2" t="n">
         <v>215</v>
@@ -27094,13 +27094,13 @@
         <v>-0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I4" t="n">
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>374.0000000001075</v>
+        <v>374</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27448,10 +27448,10 @@
         <v>400</v>
       </c>
       <c r="G2" t="n">
+        <v>398.2013121321735</v>
+      </c>
+      <c r="H2" t="n">
         <v>400</v>
-      </c>
-      <c r="H2" t="n">
-        <v>398.2013121321735</v>
       </c>
       <c r="I2" t="n">
         <v>134.2726973711268</v>
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>10.55655664632661</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>263.5820573201953</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H3" t="n">
         <v>330.0491815260438</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,16 +27557,16 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R3" t="n">
-        <v>159.6519859716246</v>
+        <v>400</v>
       </c>
       <c r="S3" t="n">
         <v>400</v>
       </c>
       <c r="T3" t="n">
-        <v>139.8336422244496</v>
+        <v>30.47344446279683</v>
       </c>
       <c r="U3" t="n">
         <v>400</v>
@@ -27600,7 +27600,7 @@
         <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>400</v>
+        <v>312.3924407734274</v>
       </c>
       <c r="F4" t="n">
         <v>274.3828559677419</v>
@@ -27609,19 +27609,19 @@
         <v>244.8599384153005</v>
       </c>
       <c r="H4" t="n">
-        <v>227.1357818393235</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
         <v>400</v>
       </c>
       <c r="J4" t="n">
-        <v>226.6105374838818</v>
+        <v>22.26478490148153</v>
       </c>
       <c r="K4" t="n">
         <v>400</v>
       </c>
       <c r="L4" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M4" t="n">
         <v>400</v>
@@ -27642,25 +27642,25 @@
         <v>400</v>
       </c>
       <c r="S4" t="n">
-        <v>400</v>
+        <v>359.1680042930194</v>
       </c>
       <c r="T4" t="n">
         <v>209.2386648669134</v>
       </c>
       <c r="U4" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y4" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="5">
@@ -27688,10 +27688,10 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>398.2013121321734</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
-        <v>134.2726973711268</v>
+        <v>132.4740095033002</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27764,13 +27764,13 @@
         <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>325.5201396486123</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>330.0491815260438</v>
+        <v>89.04075640470492</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>209.5726123064429</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27794,10 +27794,10 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R6" t="n">
-        <v>275.0816784461132</v>
+        <v>159.6519859716246</v>
       </c>
       <c r="S6" t="n">
         <v>400</v>
@@ -27806,13 +27806,13 @@
         <v>400</v>
       </c>
       <c r="U6" t="n">
+        <v>26.1959257979226</v>
+      </c>
+      <c r="V6" t="n">
         <v>400</v>
       </c>
-      <c r="V6" t="n">
-        <v>40.51066719152016</v>
-      </c>
       <c r="W6" t="n">
-        <v>58.37314290982852</v>
+        <v>400</v>
       </c>
       <c r="X6" t="n">
         <v>400</v>
@@ -27831,34 +27831,34 @@
         <v>400</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
         <v>400</v>
       </c>
       <c r="E7" t="n">
+        <v>280.9809048369565</v>
+      </c>
+      <c r="F7" t="n">
+        <v>274.3828559677419</v>
+      </c>
+      <c r="G7" t="n">
         <v>400</v>
       </c>
-      <c r="F7" t="n">
+      <c r="H7" t="n">
         <v>400</v>
-      </c>
-      <c r="G7" t="n">
-        <v>376.5799194282308</v>
-      </c>
-      <c r="H7" t="n">
-        <v>227.1357818393235</v>
       </c>
       <c r="I7" t="n">
         <v>171.1020457840527</v>
       </c>
       <c r="J7" t="n">
-        <v>22.26478490148153</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K7" t="n">
         <v>267.1509377355693</v>
       </c>
       <c r="L7" t="n">
-        <v>396.2015953708939</v>
+        <v>400</v>
       </c>
       <c r="M7" t="n">
         <v>400</v>
@@ -27879,25 +27879,25 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>359.1680042930194</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
         <v>209.2386648669134</v>
       </c>
       <c r="U7" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>346.6628438480176</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -27955,10 +27955,10 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>223.3220918649904</v>
+        <v>225.120779732817</v>
       </c>
       <c r="S8" t="n">
-        <v>400</v>
+        <v>398.2013121321733</v>
       </c>
       <c r="T8" t="n">
         <v>400</v>
@@ -27986,28 +27986,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>35.56948498147727</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>339.6362423378769</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>325.5201396486123</v>
       </c>
       <c r="H9" t="n">
         <v>330.0491815260438</v>
       </c>
       <c r="I9" t="n">
-        <v>209.5726123064429</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28031,7 +28031,7 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>145.073529241423</v>
       </c>
       <c r="R9" t="n">
         <v>400</v>
@@ -28043,7 +28043,7 @@
         <v>400</v>
       </c>
       <c r="U9" t="n">
-        <v>400</v>
+        <v>26.1959257979226</v>
       </c>
       <c r="V9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>144.7595234961632</v>
       </c>
     </row>
     <row r="10">
@@ -28065,37 +28065,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C10" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D10" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
         <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
       </c>
       <c r="H10" t="n">
+        <v>266.9645639617898</v>
+      </c>
+      <c r="I10" t="n">
         <v>400</v>
       </c>
-      <c r="I10" t="n">
-        <v>290.8681273693285</v>
-      </c>
       <c r="J10" t="n">
-        <v>22.26478490148153</v>
+        <v>396.2647849014816</v>
       </c>
       <c r="K10" t="n">
-        <v>267.1509377355693</v>
+        <v>400</v>
       </c>
       <c r="L10" t="n">
-        <v>400</v>
+        <v>396.2015953708939</v>
       </c>
       <c r="M10" t="n">
         <v>400</v>
@@ -28119,22 +28119,22 @@
         <v>359.1680042930194</v>
       </c>
       <c r="T10" t="n">
-        <v>209.2386648669134</v>
+        <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9483584875727</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="11">
@@ -28223,7 +28223,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C12" t="n">
         <v>319</v>
@@ -28232,19 +28232,19 @@
         <v>319</v>
       </c>
       <c r="E12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G12" t="n">
         <v>319</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="I12" t="n">
-        <v>189.9476123064429</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -28274,16 +28274,16 @@
         <v>319</v>
       </c>
       <c r="S12" t="n">
-        <v>96.05772723972444</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
         <v>319</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="V12" t="n">
-        <v>319</v>
+        <v>286.0053395461677</v>
       </c>
       <c r="W12" t="n">
         <v>319</v>
@@ -28460,13 +28460,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="E15" t="n">
         <v>319</v>
@@ -28475,10 +28475,10 @@
         <v>319</v>
       </c>
       <c r="G15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>189.9476123064429</v>
@@ -28529,7 +28529,7 @@
         <v>319</v>
       </c>
       <c r="Y15" t="n">
-        <v>96.05772723972444</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16">
@@ -28554,7 +28554,7 @@
         <v>319</v>
       </c>
       <c r="G16" t="n">
-        <v>319.0000000000007</v>
+        <v>319</v>
       </c>
       <c r="H16" t="n">
         <v>319</v>
@@ -28697,13 +28697,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E18" t="n">
         <v>319</v>
@@ -28745,13 +28745,13 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>319</v>
@@ -28766,7 +28766,7 @@
         <v>319</v>
       </c>
       <c r="Y18" t="n">
-        <v>96.05772723972444</v>
+        <v>96.05772723972433</v>
       </c>
     </row>
     <row r="19">
@@ -28800,7 +28800,7 @@
         <v>319</v>
       </c>
       <c r="J19" t="n">
-        <v>319.0000000000011</v>
+        <v>319</v>
       </c>
       <c r="K19" t="n">
         <v>319</v>
@@ -28903,7 +28903,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>158.20095561214</v>
+        <v>158.200955612214</v>
       </c>
       <c r="S20" t="n">
         <v>319</v>
@@ -28934,10 +28934,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D21" t="n">
         <v>319</v>
@@ -28946,7 +28946,7 @@
         <v>319</v>
       </c>
       <c r="F21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
         <v>319</v>
@@ -28988,10 +28988,10 @@
         <v>319</v>
       </c>
       <c r="T21" t="n">
-        <v>319</v>
+        <v>96.05772723972433</v>
       </c>
       <c r="U21" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
         <v>319</v>
@@ -29000,7 +29000,7 @@
         <v>319</v>
       </c>
       <c r="X21" t="n">
-        <v>96.05772723972456</v>
+        <v>319</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -29174,16 +29174,16 @@
         <v>319</v>
       </c>
       <c r="C24" t="n">
-        <v>96.05772723972427</v>
+        <v>319</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G24" t="n">
         <v>319</v>
@@ -29219,7 +29219,7 @@
         <v>72.31352924142297</v>
       </c>
       <c r="R24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>319</v>
@@ -29228,10 +29228,10 @@
         <v>319</v>
       </c>
       <c r="U24" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>319</v>
+        <v>96.05772723972427</v>
       </c>
       <c r="W24" t="n">
         <v>319</v>
@@ -29411,19 +29411,19 @@
         <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="D27" t="n">
         <v>319</v>
       </c>
       <c r="E27" t="n">
-        <v>319</v>
+        <v>96.05772723972439</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
         <v>319</v>
@@ -29462,7 +29462,7 @@
         <v>319</v>
       </c>
       <c r="T27" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
         <v>319</v>
@@ -29471,7 +29471,7 @@
         <v>319</v>
       </c>
       <c r="W27" t="n">
-        <v>96.05772723972456</v>
+        <v>319</v>
       </c>
       <c r="X27" t="n">
         <v>319</v>
@@ -29654,10 +29654,10 @@
         <v>319</v>
       </c>
       <c r="E30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="G30" t="n">
         <v>319</v>
@@ -29696,7 +29696,7 @@
         <v>319</v>
       </c>
       <c r="S30" t="n">
-        <v>96.05772723972467</v>
+        <v>0</v>
       </c>
       <c r="T30" t="n">
         <v>319</v>
@@ -29705,16 +29705,16 @@
         <v>319</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="X30" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>319</v>
+        <v>96.05772723972456</v>
       </c>
     </row>
     <row r="31">
@@ -29891,13 +29891,13 @@
         <v>319</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>319</v>
       </c>
       <c r="F33" t="n">
-        <v>96.05772723972447</v>
+        <v>319</v>
       </c>
       <c r="G33" t="n">
-        <v>319</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
         <v>319</v>
@@ -29936,7 +29936,7 @@
         <v>319</v>
       </c>
       <c r="T33" t="n">
-        <v>319</v>
+        <v>96.05772723972433</v>
       </c>
       <c r="U33" t="n">
         <v>319</v>
@@ -30125,13 +30125,13 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E36" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
         <v>324.9501396486123</v>
@@ -30140,7 +30140,7 @@
         <v>324.5441815260438</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>189.9476123064429</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -30164,10 +30164,10 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R36" t="n">
-        <v>138.0514806137321</v>
+        <v>397</v>
       </c>
       <c r="S36" t="n">
         <v>397</v>
@@ -30179,16 +30179,16 @@
         <v>397</v>
       </c>
       <c r="V36" t="n">
-        <v>397</v>
+        <v>40.51066719150012</v>
       </c>
       <c r="W36" t="n">
-        <v>397</v>
+        <v>58.37314290980848</v>
       </c>
       <c r="X36" t="n">
-        <v>397</v>
+        <v>254.9412069631577</v>
       </c>
       <c r="Y36" t="n">
-        <v>397</v>
+        <v>25.39139276611431</v>
       </c>
     </row>
     <row r="37">
@@ -30201,25 +30201,25 @@
         <v>397</v>
       </c>
       <c r="C37" t="n">
-        <v>324.9103971186021</v>
+        <v>397</v>
       </c>
       <c r="D37" t="n">
-        <v>285.5362180555555</v>
+        <v>397</v>
       </c>
       <c r="E37" t="n">
-        <v>280.9809048369565</v>
+        <v>397</v>
       </c>
       <c r="F37" t="n">
-        <v>274.3828559677419</v>
+        <v>397</v>
       </c>
       <c r="G37" t="n">
-        <v>244.3820695628415</v>
+        <v>397</v>
       </c>
       <c r="H37" t="n">
-        <v>222.8870933147334</v>
+        <v>397</v>
       </c>
       <c r="I37" t="n">
-        <v>156.7312261119215</v>
+        <v>163.4319369905253</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -30228,7 +30228,7 @@
         <v>211.6312656044217</v>
       </c>
       <c r="L37" t="n">
-        <v>325.1555297971234</v>
+        <v>397</v>
       </c>
       <c r="M37" t="n">
         <v>397</v>
@@ -30249,25 +30249,25 @@
         <v>397</v>
       </c>
       <c r="S37" t="n">
-        <v>350.8400534733473</v>
+        <v>397</v>
       </c>
       <c r="T37" t="n">
         <v>207.1968615882249</v>
       </c>
       <c r="U37" t="n">
-        <v>397</v>
+        <v>150.9222929138022</v>
       </c>
       <c r="V37" t="n">
-        <v>397</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W37" t="n">
-        <v>397</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X37" t="n">
-        <v>397</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y37" t="n">
-        <v>397</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="38">
@@ -30356,25 +30356,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>10.55655664621921</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C39" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>202.9182143729445</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
-        <v>339.6362423378769</v>
+        <v>164.4344330377232</v>
       </c>
       <c r="G39" t="n">
         <v>324.9501396486123</v>
       </c>
       <c r="H39" t="n">
-        <v>324.5441815260438</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
         <v>189.9476123064429</v>
@@ -30419,10 +30419,10 @@
         <v>397</v>
       </c>
       <c r="W39" t="n">
-        <v>58.37314290972117</v>
+        <v>397</v>
       </c>
       <c r="X39" t="n">
-        <v>45.8627394452802</v>
+        <v>397</v>
       </c>
       <c r="Y39" t="n">
         <v>397</v>
@@ -30447,19 +30447,19 @@
         <v>280.9809048369565</v>
       </c>
       <c r="F40" t="n">
-        <v>397</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G40" t="n">
         <v>397</v>
       </c>
       <c r="H40" t="n">
-        <v>222.8870933147334</v>
+        <v>397</v>
       </c>
       <c r="I40" t="n">
-        <v>397</v>
+        <v>156.7312261119215</v>
       </c>
       <c r="J40" t="n">
-        <v>334.8243561321077</v>
+        <v>362.4794570326746</v>
       </c>
       <c r="K40" t="n">
         <v>397</v>
@@ -30486,10 +30486,10 @@
         <v>397</v>
       </c>
       <c r="S40" t="n">
-        <v>350.8400534733473</v>
+        <v>397</v>
       </c>
       <c r="T40" t="n">
-        <v>207.1968615882249</v>
+        <v>322.1548253960752</v>
       </c>
       <c r="U40" t="n">
         <v>150.9222929138022</v>
@@ -30638,7 +30638,7 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>69.92675579555282</v>
+        <v>72.31352924142297</v>
       </c>
       <c r="R42" t="n">
         <v>293</v>
@@ -30647,7 +30647,7 @@
         <v>293</v>
       </c>
       <c r="T42" t="n">
-        <v>293</v>
+        <v>290.6132265545748</v>
       </c>
       <c r="U42" t="n">
         <v>293</v>
@@ -30875,7 +30875,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>69.92675579555282</v>
+        <v>69.92675579599782</v>
       </c>
       <c r="R45" t="n">
         <v>293</v>
@@ -34743,10 +34743,10 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>242.0199542155221</v>
+        <v>374</v>
       </c>
       <c r="K2" t="n">
-        <v>52.15992964824119</v>
+        <v>373.9999999999999</v>
       </c>
       <c r="L2" t="n">
         <v>64.70900502512563</v>
@@ -34755,16 +34755,16 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
+        <v>235.5012052109774</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
+        <v>58.67867865278593</v>
+      </c>
+      <c r="Q2" t="n">
         <v>374</v>
-      </c>
-      <c r="O2" t="n">
-        <v>374</v>
-      </c>
-      <c r="P2" t="n">
-        <v>374</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0</v>
       </c>
       <c r="R2" t="n">
         <v>0</v>
@@ -34886,7 +34886,7 @@
         <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>119.0190951630435</v>
+        <v>31.41153593647087</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -34895,19 +34895,19 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I4" t="n">
         <v>228.8979542159473</v>
       </c>
       <c r="J4" t="n">
-        <v>204.3457525824002</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
         <v>132.8490622644307</v>
       </c>
       <c r="L4" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -34928,25 +34928,25 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>40.83199570698065</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -34983,25 +34983,25 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>235.5012052109774</v>
+        <v>52.1599296482412</v>
       </c>
       <c r="L5" t="n">
-        <v>64.70900502512563</v>
+        <v>64.70900502512562</v>
       </c>
       <c r="M5" t="n">
-        <v>374</v>
+        <v>242.0199542155221</v>
       </c>
       <c r="N5" t="n">
         <v>374</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="P5" t="n">
-        <v>58.67867865278593</v>
+        <v>374</v>
       </c>
       <c r="Q5" t="n">
-        <v>374</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35117,34 +35117,34 @@
         <v>112.8861996629213</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
         <v>114.4637819444445</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>131.7199810129302</v>
+        <v>155.1400615846995</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>172.8642181606765</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.798404629106074</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -35165,25 +35165,25 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>40.83199570698063</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>147.4925336318014</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35217,16 +35217,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K8" t="n">
-        <v>374</v>
+        <v>52.15992964824119</v>
       </c>
       <c r="L8" t="n">
         <v>64.70900502512563</v>
       </c>
       <c r="M8" t="n">
-        <v>374</v>
+        <v>183.3412755627362</v>
       </c>
       <c r="N8" t="n">
         <v>374</v>
@@ -35238,7 +35238,7 @@
         <v>58.67867865278593</v>
       </c>
       <c r="Q8" t="n">
-        <v>235.5012052109774</v>
+        <v>374</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -35351,37 +35351,37 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>155.1400615846995</v>
       </c>
       <c r="H10" t="n">
-        <v>172.8642181606765</v>
+        <v>39.82878212246631</v>
       </c>
       <c r="I10" t="n">
-        <v>119.7660815852758</v>
+        <v>228.8979542159473</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>374</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>132.8490622644307</v>
       </c>
       <c r="L10" t="n">
-        <v>3.798404629106074</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -35405,22 +35405,22 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>190.7613351330866</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>249.0516415124273</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -35454,28 +35454,28 @@
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K11" t="n">
-        <v>187.6734723618091</v>
+        <v>358.1785587780531</v>
       </c>
       <c r="L11" t="n">
-        <v>655</v>
+        <v>232.8255376884422</v>
       </c>
       <c r="M11" t="n">
-        <v>185.1688643668499</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>655</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>178.3365374610834</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="P11" t="n">
-        <v>211.8739801603236</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>602.3534944697265</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35615,7 +35615,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K13" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35691,19 +35691,19 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>520.4824991852875</v>
+        <v>90.1777625991308</v>
       </c>
       <c r="K14" t="n">
-        <v>654.9999999999999</v>
+        <v>655</v>
       </c>
       <c r="L14" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="N14" t="n">
-        <v>192.6633045704905</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>178.3365374610834</v>
@@ -35712,7 +35712,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q14" t="n">
-        <v>602.3534944697265</v>
+        <v>570.3215356263728</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -35840,7 +35840,7 @@
         <v>44.61714403225807</v>
       </c>
       <c r="G16" t="n">
-        <v>74.61793043715923</v>
+        <v>74.61793043715849</v>
       </c>
       <c r="H16" t="n">
         <v>96.11290668526664</v>
@@ -35937,10 +35937,10 @@
         <v>654.9999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>655</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="N17" t="n">
-        <v>13.1201064832801</v>
+        <v>615.4736009530061</v>
       </c>
       <c r="O17" t="n">
         <v>178.3365374610834</v>
@@ -35949,7 +35949,7 @@
         <v>211.8739801603236</v>
       </c>
       <c r="Q17" t="n">
-        <v>602.3534944697265</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36086,7 +36086,7 @@
         <v>162.2687738880785</v>
       </c>
       <c r="J19" t="n">
-        <v>330.520542967372</v>
+        <v>330.5205429673709</v>
       </c>
       <c r="K19" t="n">
         <v>107.3687343955783</v>
@@ -36168,19 +36168,19 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K20" t="n">
-        <v>655</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L20" t="n">
-        <v>654.9999999999999</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M20" t="n">
-        <v>655.0000000000038</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="N20" t="n">
-        <v>148.1470733148863</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="O20" t="n">
-        <v>178.3365374610834</v>
+        <v>560.9846007256465</v>
       </c>
       <c r="P20" t="n">
         <v>211.8739801603236</v>
@@ -36189,7 +36189,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-6.693654731803091e-11</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36326,7 +36326,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K22" t="n">
-        <v>107.3687343955783</v>
+        <v>107.3687343955782</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -36402,25 +36402,25 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>90.1777625991308</v>
+        <v>520.4824991852875</v>
       </c>
       <c r="K23" t="n">
+        <v>187.6734723618091</v>
+      </c>
+      <c r="L23" t="n">
         <v>655</v>
       </c>
-      <c r="L23" t="n">
-        <v>654.9999999999999</v>
-      </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>397.0428445271731</v>
       </c>
       <c r="N23" t="n">
-        <v>360.0210534751301</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
         <v>178.3365374610834</v>
       </c>
       <c r="P23" t="n">
-        <v>655.0000000000092</v>
+        <v>655.0000000000006</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -36648,16 +36648,16 @@
         <v>232.8255376884422</v>
       </c>
       <c r="M26" t="n">
-        <v>655.0000000000165</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>4.989832209118522</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>178.3365374610834</v>
+        <v>655.0000000000001</v>
       </c>
       <c r="P26" t="n">
-        <v>211.8739801603236</v>
+        <v>395.200349830088</v>
       </c>
       <c r="Q26" t="n">
         <v>602.3534944697265</v>
@@ -36800,7 +36800,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K28" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -36879,13 +36879,13 @@
         <v>520.4824991852875</v>
       </c>
       <c r="K29" t="n">
-        <v>655.0000000001147</v>
+        <v>187.6734723618091</v>
       </c>
       <c r="L29" t="n">
-        <v>232.8255376884422</v>
+        <v>655</v>
       </c>
       <c r="M29" t="n">
-        <v>655.0000000000276</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -36894,10 +36894,10 @@
         <v>178.3365374610834</v>
       </c>
       <c r="P29" t="n">
-        <v>351.8907792008521</v>
+        <v>655.0000000000028</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>397.0428445271708</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>330.5205429673709</v>
       </c>
       <c r="K31" t="n">
-        <v>107.3687343955782</v>
+        <v>107.3687343955783</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37116,25 +37116,25 @@
         <v>90.1777625991308</v>
       </c>
       <c r="K32" t="n">
-        <v>655.0000000001146</v>
+        <v>187.673472361809</v>
       </c>
       <c r="L32" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M32" t="n">
-        <v>655.0000000000401</v>
+        <v>655.0000000000038</v>
       </c>
       <c r="N32" t="n">
-        <v>127.1955157869561</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>178.3365374610834</v>
+        <v>655.0000000000038</v>
       </c>
       <c r="P32" t="n">
-        <v>655.0000000000401</v>
+        <v>211.8739801603236</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>560.9846007256402</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37356,16 +37356,16 @@
         <v>187.673472361809</v>
       </c>
       <c r="L35" t="n">
-        <v>232.8255376884422</v>
+        <v>243.1636737675854</v>
       </c>
       <c r="M35" t="n">
-        <v>374.0000000000728</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="N35" t="n">
-        <v>206.0015986183266</v>
+        <v>0</v>
       </c>
       <c r="O35" t="n">
-        <v>178.3365374610834</v>
+        <v>374.0000000000201</v>
       </c>
       <c r="P35" t="n">
         <v>211.8739801603236</v>
@@ -37435,19 +37435,19 @@
         <v>318.5740338860743</v>
       </c>
       <c r="L36" t="n">
-        <v>374.0000000000728</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M36" t="n">
-        <v>156.7422489185003</v>
+        <v>286.9650421645043</v>
       </c>
       <c r="N36" t="n">
-        <v>339.9353519954473</v>
+        <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>46.59266649806909</v>
+        <v>353.753087725394</v>
       </c>
       <c r="P36" t="n">
-        <v>45.25534927787736</v>
+        <v>264.4060611184268</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -37487,25 +37487,25 @@
         <v>109.8861996629213</v>
       </c>
       <c r="C37" t="n">
-        <v>52.1851504705574</v>
+        <v>124.2747533519553</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>111.4637819444445</v>
       </c>
       <c r="E37" t="n">
-        <v>0</v>
+        <v>116.0190951630435</v>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>122.6171440322581</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>152.6179304371585</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>174.1129066852666</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>6.700710878603809</v>
       </c>
       <c r="J37" t="n">
         <v>11.52054296737091</v>
@@ -37514,7 +37514,7 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>71.84447020287655</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
@@ -37535,25 +37535,25 @@
         <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>46.15994652665273</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
       </c>
       <c r="U37" t="n">
-        <v>246.0777070861978</v>
+        <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>197.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>170.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>149.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>109.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -37593,13 +37593,13 @@
         <v>187.673472361809</v>
       </c>
       <c r="L38" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M38" t="n">
-        <v>374.0000000001074</v>
+        <v>206.0015986180542</v>
       </c>
       <c r="N38" t="n">
-        <v>206.0015986184463</v>
+        <v>374.0000000000455</v>
       </c>
       <c r="O38" t="n">
         <v>178.3365374610834</v>
@@ -37666,25 +37666,25 @@
         <v>0</v>
       </c>
       <c r="J39" t="n">
-        <v>146.2959740897275</v>
+        <v>199.7892383131474</v>
       </c>
       <c r="K39" t="n">
-        <v>22.69379302306083</v>
+        <v>318.5740338860743</v>
       </c>
       <c r="L39" t="n">
-        <v>374.0000000001074</v>
+        <v>57.40142568134173</v>
       </c>
       <c r="M39" t="n">
-        <v>286.9650421645043</v>
+        <v>145.9334897349552</v>
       </c>
       <c r="N39" t="n">
         <v>339.9353519954473</v>
       </c>
       <c r="O39" t="n">
-        <v>46.59266649806909</v>
+        <v>374.0000000000455</v>
       </c>
       <c r="P39" t="n">
-        <v>264.4060611184268</v>
+        <v>45.25534927787736</v>
       </c>
       <c r="Q39" t="n">
         <v>0</v>
@@ -37733,19 +37733,19 @@
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>122.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
         <v>152.6179304371585</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>174.1129066852666</v>
       </c>
       <c r="I40" t="n">
-        <v>240.2687738880785</v>
+        <v>0</v>
       </c>
       <c r="J40" t="n">
-        <v>346.3448990994786</v>
+        <v>374.0000000000455</v>
       </c>
       <c r="K40" t="n">
         <v>185.3687343955783</v>
@@ -37772,10 +37772,10 @@
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>46.15994652665276</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>114.9579638078503</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
@@ -37824,19 +37824,19 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>90.1777625991308</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="K41" t="n">
         <v>187.673472361809</v>
       </c>
       <c r="L41" t="n">
-        <v>232.8255376884422</v>
+        <v>374</v>
       </c>
       <c r="M41" t="n">
-        <v>206.0015986183863</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
-        <v>374.0000000001674</v>
+        <v>155.0048989056036</v>
       </c>
       <c r="O41" t="n">
         <v>178.3365374610834</v>
@@ -37903,22 +37903,22 @@
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>199.7892383131474</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L42" t="n">
-        <v>57.40142568134173</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="M42" t="n">
         <v>286.9650421645043</v>
       </c>
       <c r="N42" t="n">
-        <v>307.1604212277793</v>
+        <v>158.8239925827586</v>
       </c>
       <c r="O42" t="n">
-        <v>46.59266649806909</v>
+        <v>374.0000000000692</v>
       </c>
       <c r="P42" t="n">
         <v>264.4060611184268</v>
@@ -38061,22 +38061,22 @@
         <v>0</v>
       </c>
       <c r="J44" t="n">
-        <v>90.1777625991308</v>
+        <v>374.0000000001529</v>
       </c>
       <c r="K44" t="n">
-        <v>187.673472361809</v>
+        <v>374</v>
       </c>
       <c r="L44" t="n">
-        <v>232.8255376884422</v>
+        <v>232.8255376884423</v>
       </c>
       <c r="M44" t="n">
-        <v>374.0000000001147</v>
+        <v>0</v>
       </c>
       <c r="N44" t="n">
-        <v>206.0015986184391</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
-        <v>178.3365374610834</v>
+        <v>288.1893710399702</v>
       </c>
       <c r="P44" t="n">
         <v>211.8739801603236</v>
@@ -38143,10 +38143,10 @@
         <v>199.7892383131474</v>
       </c>
       <c r="K45" t="n">
-        <v>318.5740338860743</v>
+        <v>22.69379302306083</v>
       </c>
       <c r="L45" t="n">
-        <v>203.3349154166819</v>
+        <v>374.0000000001529</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -38155,10 +38155,10 @@
         <v>339.9353519954473</v>
       </c>
       <c r="O45" t="n">
-        <v>374.0000000001147</v>
+        <v>280.0644444386536</v>
       </c>
       <c r="P45" t="n">
-        <v>45.25534927787736</v>
+        <v>264.4060611184268</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
